--- a/briefing-hppc/briefing_hppc_leite_de_rosas.xlsx
+++ b/briefing-hppc/briefing_hppc_leite_de_rosas.xlsx
@@ -290,7 +290,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="1135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="1104">
   <si>
     <t xml:space="preserve">LEITE DE ROSAS  |  BRIEFING DE DESENVOLVIMENTO DE PRODUTO — HPPC</t>
   </si>
@@ -595,43 +595,43 @@
     <t xml:space="preserve">Código do projeto</t>
   </si>
   <si>
-    <t xml:space="preserve">Padrão BRF_&lt;ano&gt;_&lt;nº sequencial&gt;. Ex.: BRF_2026_004.</t>
+    <t xml:space="preserve">Padrão BRF_&lt;ano&gt;_&lt;nº com 3 dígitos&gt;. Ex.: BRF_2026_004. No formulário HTML ele é gerado sozinho; aqui, copie o código de lá.</t>
   </si>
   <si>
     <t xml:space="preserve">Nome de trabalho</t>
   </si>
   <si>
-    <t xml:space="preserve">Nome interno, não é o nome comercial. Ex.: 'Desodorante Creme Sensitive'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marca / arquitetura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leite de Rosas (extensão), Leite de Rosas sub-marca, marca do portfólio ou marca nova.</t>
+    <t xml:space="preserve">Nome interno, só para a equipe conversar sobre o projeto. O nome comercial é decidido depois. Ex.: 'Roll-on Leite de Rosas 50 ml'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leite de Rosas | Barla | Sub-marca de uma delas | Outra marca do portfólio | Marca nova. Nos três últimos casos, escreva ao lado qual é o nome.</t>
   </si>
   <si>
     <t xml:space="preserve">Categoria HPPC</t>
   </si>
   <si>
-    <t xml:space="preserve">Desodorante, higiene corporal, cuidado facial, cabelos, infantil, perfumaria, higiene íntima etc.</t>
+    <t xml:space="preserve">Desodorante | Talco | Higiene corporal | Cuidado facial | Cabelos | Infantil | Perfumaria | Higiene íntima | Outra (escreva qual).</t>
   </si>
   <si>
     <t xml:space="preserve">Tipo de projeto</t>
   </si>
   <si>
-    <t xml:space="preserve">Novo produto | Extensão de linha | Renovação de fórmula | Novo tamanho | Restyling de embalagem | Redução de custo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solicitante / área</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quem abriu a demanda e a área responsável pela defesa do projeto no gate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrocinador (Diretoria)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretor que responde pelo projeto perante a Diretoria Executiva.</t>
+    <t xml:space="preserve">Novo produto | Extensão de linha | Renovação de fórmula | Novo tamanho | Restyling de embalagem | Redução de custo | Outro (descreva).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Em que ponto o projeto está hoje</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Ideia (nada validado) | 2 Conceito (escrito, sem fórmula) | 3 Viabilidade (custo e mercado estimados) | 4 Desenvolvimento (fórmula em teste) | 5 Industrialização (lote piloto) | 6 Lançamento (pronto para vender). Serve para o comitê saber o que já foi feito e o que falta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prioridade declarada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alta | Média | Baixa. Alta significa passar na frente dos outros na fila do laboratório e da fábrica — use com parcimônia. Prioridade declarada é hipótese; o Scorecard (aba 7) é o que vale.</t>
   </si>
   <si>
     <t xml:space="preserve">Data de abertura</t>
@@ -640,127 +640,109 @@
     <t xml:space="preserve">Data em que o briefing foi aberto.</t>
   </si>
   <si>
-    <t xml:space="preserve">Gate atual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G0 Ideia | G1 Conceito | G2 Viabilidade | G3 Desenvolvimento | G4 Industrialização | G5 Lançamento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prioridade declarada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alta | Média | Baixa. Prioridade declarada é hipótese; o Scorecard (aba 7) é o que vale.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2 CONTEXTO E RACIONAL — POR QUE ESTE PRODUTO, POR QUE AGORA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Problema ou oportunidade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uma frase objetiva. O que existe hoje no mercado ou no consumidor que justifica gastar dinheiro nisso.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Por que agora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gatilho de timing: mudança de hábito, movimento de concorrente, janela de canal, sazonalidade, mudança regulatória.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Encaixe estratégico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como reduz a concentração de faturamento em poucos SKUs, ou como defende o carro-chefe.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O que acontece se não fizermos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O custo de não fazer. Se a resposta for 'nada', o projeto provavelmente não deveria existir.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alavanca da marca usada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Que ativo da Leite de Rosas o produto empresta: reconhecimento, território de frescor/cuidado, o rosa, tradição, distribuição.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3 OBJETIVO E METAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Objetivo do produto (1 frase)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comece com um verbo. Ex.: 'Capturar o consumidor de pele sensível que hoje troca a marca por dermocosmético'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meta de volume — Ano 1 (un.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unidades vendidas no primeiro ano cheio. Este número alimenta a aba 6.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meta de receita líquida — Ano 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deve bater com o resultado calculado na aba 6. Se não bater, uma das duas premissas está errada.</t>
+    <t xml:space="preserve">1.2 POR QUE ESTE PROJETO EXISTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Que problema ou oportunidade este produto resolve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descreva o problema do negócio ou do consumidor, não a solução — a solução é o produto e vem depois. Ex.: 'não temos roll-on, que é o formato que mais cresce no Nordeste, onde somos fortes'. Mínimo de 80 caracteres.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por que agora, e não daqui a dois anos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precisa existir um gatilho concreto: concorrente que se mexeu, canal pedindo, regra que mudou, sazonalidade, oportunidade de matéria-prima. Mínimo de 60 caracteres.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como isso ajuda a empresa como um todo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duas respostas costumam ser boas: reduz a dependência dos poucos produtos que sustentam a receita, ou protege o carro-chefe de um ataque de concorrente. Mínimo de 60 caracteres.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O que acontece se a gente não fizer nada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se a resposta honesta for 'nada acontece', o projeto não deveria existir. Melhor descobrir agora do que depois de gastar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3 O QUE PRECISA ENTREGAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Objetivo do produto em uma frase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junte numa frase o que o produto faz e quanto precisa entregar. Ex.: 'colocar a Leite de Rosas no roll-on com um item de entrada, vendendo 400 mil unidades com 32% de margem no primeiro ano'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta de volume no Ano 1 (un.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantas unidades vendidas no primeiro ano cheio. Use o número que você defenderia numa reunião, não o otimista. Alimenta a aba 6.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta de receita líquida no Ano 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receita já sem impostos e sem descontos comerciais. Deve bater com o resultado da aba 6; se não bater, uma das duas premissas está errada.</t>
   </si>
   <si>
     <t xml:space="preserve">Margem de contribuição-alvo (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">Piso de margem aceitável para o projeto seguir. Digite como percentual (ex.: 35%).</t>
+    <t xml:space="preserve">De cada R$ 100 vendidos, quanto sobra depois de custo do produto, impostos, comissão e frete. É o piso para o projeto seguir. Digite como percentual (ex.: 35%).</t>
   </si>
   <si>
     <t xml:space="preserve">Distribuição-alvo (nº de PDVs)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pontos de venda ativos ao fim do Ano 1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4 CONSUMIDOR E OCASIÃO DE USO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Público-alvo primário</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demografia + comportamento. Demografia sozinha não é público-alvo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Público-alvo secundário</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quem também compra, mas não é para quem a comunicação fala.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ocasião e frequência de uso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quando, onde, quantas vezes. Define tamanho de embalagem e giro.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dor / tensão do consumidor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A frustração real com as soluções atuais, na linguagem do consumidor.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A verdade não óbvia que conecta a dor ao produto. Se soa como slogan, ainda não é insight.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barreira de adoção esperada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preço, ceticismo quanto ao benefício, hábito consolidado, percepção de marca. E como derrubar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5 CONCEITO DE PRODUTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conceito em uma frase</t>
+    <t xml:space="preserve">Em quantas lojas o produto precisa estar no fim do Ano 1. Ex.: 8.000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capex máximo autorizado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teto de investimento em máquina e ferramental para este projeto. A aba 6 compara o investimento total com este teto e avisa se estourou. Deixe em branco se ainda não houver teto definido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4 PARA QUEM É E QUANDO SE USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quem é a pessoa que vai comprar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idade e classe social sozinhas não são público-alvo. Diga também como essa pessoa compra e o que valoriza. Ex.: 'mulheres de 30 a 55 anos, classes C e D do Nordeste, que fazem a compra grande no atacarejo uma vez por mês'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quando e com que frequência ela usa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A frequência define o tamanho da embalagem e o volume comprado por ano — números que voltam na aba 2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qual é o incômodo que ela tem hoje</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escreva como a própria pessoa falaria, não em linguagem de marketing. Ex.: 'transpira muito no calor e os desodorantes que cabem no orçamento dela mancham a blusa'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A virada por trás dessa dor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O que está por baixo da dor e que ninguém na categoria está dizendo. Se a frase parece um slogan, ainda não é insight.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O que faria essa pessoa não comprar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antecipar a objeção agora é mais barato do que descobri-la na pesquisa de conceito. Preço, ceticismo quanto ao benefício, hábito consolidado, percepção de marca.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5 O PRODUTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O produto em uma frase</t>
   </si>
   <si>
     <t xml:space="preserve">O que é, para quem, e o que entrega de diferente. Uma frase, sem adjetivo vazio.</t>
@@ -769,55 +751,49 @@
     <t xml:space="preserve">Benefício principal</t>
   </si>
   <si>
-    <t xml:space="preserve">Um só. O que o consumidor lembraria 3 dias depois.</t>
+    <t xml:space="preserve">Um só. É o que a pessoa lembraria três dias depois de usar.</t>
   </si>
   <si>
     <t xml:space="preserve">Benefícios secundários</t>
   </si>
   <si>
-    <t xml:space="preserve">No máximo dois. O terceiro dilui os outros.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reason to believe (RTB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Por que acreditar: ativo, concentração, tecnologia, teste comprobatório, 96 anos de marca.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ativos / ingredientes-chave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nome INCI e função. Marcar o que for claim-driver, pois exige comprovação.</t>
+    <t xml:space="preserve">No máximo dois. O terceiro dilui os outros e ninguém guarda.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por que acreditar nisso (RTB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O motivo técnico que sustenta o benefício: ativo, concentração, tecnologia, teste comprobatório. É o que Assuntos Regulatórios cobra para liberar o claim.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ativos e ingredientes-chave (INCI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nome INCI e função. Marque o que sustenta claim, pois exige comprovação.</t>
   </si>
   <si>
     <t xml:space="preserve">Claims pretendidos</t>
   </si>
   <si>
-    <t xml:space="preserve">Liste separando os claims de rotulagem dos claims publicitários. Cada um precisa de lastro (aba 3).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensorial alvo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Textura, absorção, toque residual, cor, fragrância e intensidade.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tamanhos / apresentações</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grama­tura(s) e por que essa(s). Amarrar com ocasião de uso e preço de gôndola.</t>
+    <t xml:space="preserve">Separe os claims de rótulo dos de publicidade. Cada um precisa de um teste que o comprove (aba 3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como tem que ser ao usar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Textura, tempo de secagem, toque que fica, cor, perfume e intensidade. É isto que o laboratório mede nos testes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamanhos e apresentações</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gramatura(s) e por quê. Amarre com a ocasião de uso e com o preço de gôndola.</t>
   </si>
   <si>
     <t xml:space="preserve">Produto de referência (benchmark)</t>
   </si>
   <si>
-    <t xml:space="preserve">O produto que o consumidor usaria no lugar deste. Serve de âncora sensorial e de preço.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O que este produto NÃO é</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delimitação explícita. Evita que o escopo cresça no meio do desenvolvimento.</t>
+    <t xml:space="preserve">O produto que serve de régua para desempenho e preço. Compre um e deixe na mesa do laboratório.</t>
   </si>
   <si>
     <t xml:space="preserve">1.6 POSICIONAMENTO, PREÇO E CANAL</t>
@@ -826,25 +802,19 @@
     <t xml:space="preserve">Posicionamento em uma frase</t>
   </si>
   <si>
-    <t xml:space="preserve">Para &lt;público&gt;, &lt;produto&gt; é a &lt;categoria&gt; que &lt;benefício&gt; porque &lt;RTB&gt;.</t>
+    <t xml:space="preserve">Complete este modelo: PARA [quem compra], O [nosso produto] É O [tipo de produto] QUE [o que faz de melhor], PORQUE [o motivo que faz acreditar].</t>
   </si>
   <si>
     <t xml:space="preserve">Faixa de preço pretendida</t>
   </si>
   <si>
-    <t xml:space="preserve">Popular | Mainstream | Premium acessível | Premium. Coerente com marca e canal.</t>
+    <t xml:space="preserve">Popular | Mainstream | Premium acessível | Premium. Mainstream é preço parecido com o do líder da categoria.</t>
   </si>
   <si>
     <t xml:space="preserve">Canal prioritário</t>
   </si>
   <si>
-    <t xml:space="preserve">Farma | Atacarejo | Supermercado | Varejo tradicional | Distribuidor | E-commerce/marketplace | Perfumaria.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canais secundários</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Onde entra depois, e em que ordem.</t>
+    <t xml:space="preserve">Farma | Atacarejo | Supermercado | Varejo tradicional | Distribuidor | E-commerce/marketplace | Perfumaria | Outros (escreva qual). É o canal onde o produto precisa dar certo primeiro; ele define embalagem, tamanho e política de preço.</t>
   </si>
   <si>
     <t xml:space="preserve">Regiões prioritárias</t>
@@ -853,73 +823,37 @@
     <t xml:space="preserve">Onde a distribuição já é forte tende a ser onde o lançamento custa menos.</t>
   </si>
   <si>
-    <t xml:space="preserve">Quais SKUs próprios podem perder volume, e qual perda é aceitável.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7 RESTRIÇÕES E CONDIÇÕES DE CONTORNO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Make or buy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produção interna | Terceirização (co-packer) | Híbrido. Terceirizar preserva caixa e acelera; interna dilui fixo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capex máximo autorizado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teto de investimento em ativo e ferramental. Confrontar com a aba 6.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prazo máximo até o lançamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Em meses. Confrontar com o cronograma da aba 8.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restrições fabris / logísticas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limitações de linha, envase, capacidade, paletização, armazenagem.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restrições regulatórias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grau de risco, exigência de registro ou notificação, claims que demandam comprovação.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restrições de marca / jurídico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registro de marca, colidência, uso do rosa institucional, trade dress.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8 MÉTRICAS DE SUCESSO E CRITÉRIO DE MORTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPI primário</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uma métrica só. Ex.: unidades/mês no 6º mês; margem de contribuição %; nº de PDVs ativos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPIs secundários</t>
+    <t xml:space="preserve">Quanto de venda nossa este produto vai tirar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todo lançamento rouba alguma venda de dentro de casa. Diga de qual produto nosso ele vai tirar, quanto aceitamos perder e por que compensa. Se a resposta for 'nenhuma', quase sempre é porque ainda não foi pensado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7 COMO SABEREMOS QUE DEU CERTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicador principal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Um só, com número e data. Ex.: '400 mil unidades vendidas até dez/2027'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicadores secundários</t>
   </si>
   <si>
     <t xml:space="preserve">No máximo três, com meta numérica e data.</t>
   </si>
   <si>
-    <t xml:space="preserve">Critério de kill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A condição objetiva que encerra o projeto. Definida antes, não depois. Ex.: 'MC &lt; 25% no teste de custo real'.</t>
+    <t xml:space="preserve">Em que situação encerramos o projeto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uma condição objetiva, com número, escrita ANTES de começar. Ex.: 'se o custo industrial passar de R$ 3,20/un. ou a intenção de compra ficar abaixo de 60%, o projeto para'. Depois que o time se apega ao projeto, ninguém mais consegue definir isso com isenção.</t>
   </si>
   <si>
     <t xml:space="preserve">Data da primeira revisão</t>
   </si>
   <si>
-    <t xml:space="preserve">Quando o time volta a olhar os KPIs com o produto na rua.</t>
+    <t xml:space="preserve">Quando o time volta a olhar os indicadores com o produto na rua.</t>
   </si>
   <si>
     <t xml:space="preserve">1.9 PAINEL CONSOLIDADO — CALCULADO PELAS DEMAIS ABAS</t>
@@ -1177,9 +1111,6 @@
     <t xml:space="preserve">2.2 BENCHMARK COMPETITIVO — O QUE O CONSUMIDOR COMPRA HOJE</t>
   </si>
   <si>
-    <t xml:space="preserve">Marca</t>
-  </si>
-  <si>
     <t xml:space="preserve">SKU / descrição</t>
   </si>
   <si>
@@ -3121,7 +3052,7 @@
     <t xml:space="preserve">Aderência à estratégia e à marca</t>
   </si>
   <si>
-    <t xml:space="preserve">5 = usa o território da Leite de Rosas sem forçar. 1 = marca não tem autoridade nenhuma nessa promessa.</t>
+    <t xml:space="preserve">5 = usa o território da Leite de Rosas sem forçar. 1 = a marca não tem autoridade nenhuma nessa promessa.</t>
   </si>
   <si>
     <t xml:space="preserve">Tamanho da oportunidade (SOM)</t>
@@ -3133,49 +3064,25 @@
     <t xml:space="preserve">Margem de contribuição</t>
   </si>
   <si>
-    <t xml:space="preserve">Ancorar no percentual da aba 5. 5 = bem acima da margem média da casa. 1 = abaixo do alvo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Investimento requerido (quanto menor, melhor)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 = quase sem capex, roda em ativo existente ou terceirizado. 1 = exige linha nova.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Velocidade até o mercado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 = na gôndola em até 6 meses. 1 = mais de 18 meses.</t>
+    <t xml:space="preserve">Ancorar no percentual da aba 5. 5 = bem acima da margem média da casa. 1 = abaixo do alvo do briefing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Força do conceito para o consumidor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ancorar em teste de conceito. 5 = intenção de compra alta e benefício claro. 1 = ninguém entendeu.</t>
   </si>
   <si>
     <t xml:space="preserve">Complexidade técnica e regulatória (quanto menor, melhor)</t>
   </si>
   <si>
-    <t xml:space="preserve">5 = fórmula conhecida, grau de risco 1. 1 = tecnologia nova e registro exigido.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sinergia fabril e logística</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 = mesma linha, mesmo fornecedor, mesma caixa. 1 = tudo novo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Força do conceito para o consumidor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ancorar em teste de conceito. 5 = intenção de compra alta e benefício claro. 1 = ninguém entendeu.</t>
+    <t xml:space="preserve">5 = fórmula conhecida, grau de risco 1, sem registro. 1 = tecnologia nova e registro exigido.</t>
   </si>
   <si>
     <t xml:space="preserve">Baixo risco de canibalização (quanto menor, melhor)</t>
   </si>
   <si>
-    <t xml:space="preserve">5 = volume vem de fora da casa. 1 = tira volume direto do carro-chefe.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sustentabilidade da vantagem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 = difícil de copiar em 12 meses. 1 = concorrente replica em um trimestre.</t>
+    <t xml:space="preserve">5 = o volume vem de fora de casa. 1 = tira volume direto do carro-chefe.</t>
   </si>
   <si>
     <t xml:space="preserve">Soma dos pesos</t>
@@ -4967,7 +4874,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1025</v>
+        <v>994</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4981,7 +4888,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1026</v>
+        <v>995</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4995,7 +4902,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>1027</v>
+        <v>996</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -5012,31 +4919,31 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1028</v>
+        <v>997</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1029</v>
+        <v>998</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>1030</v>
+        <v>999</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>1031</v>
+        <v>1000</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>1032</v>
+        <v>1001</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>1033</v>
+        <v>1002</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>1034</v>
+        <v>1003</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>357</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5044,10 +4951,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1035</v>
+        <v>1004</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>1036</v>
+        <v>1005</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
@@ -5068,10 +4975,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1037</v>
+        <v>1006</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>1038</v>
+        <v>1007</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
@@ -5092,10 +4999,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1039</v>
+        <v>1008</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1040</v>
+        <v>1009</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
@@ -5116,10 +5023,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1041</v>
+        <v>1010</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1042</v>
+        <v>1011</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
@@ -5140,10 +5047,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1043</v>
+        <v>1012</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>908</v>
+        <v>885</v>
       </c>
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
@@ -5164,10 +5071,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1044</v>
+        <v>1013</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>1045</v>
+        <v>1014</v>
       </c>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
@@ -5188,10 +5095,10 @@
         <v>7</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1046</v>
+        <v>1015</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>1047</v>
+        <v>1016</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
@@ -5212,10 +5119,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1048</v>
+        <v>1017</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>1049</v>
+        <v>1018</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
@@ -5236,10 +5143,10 @@
         <v>9</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1050</v>
+        <v>1019</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>1051</v>
+        <v>1020</v>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
@@ -5260,10 +5167,10 @@
         <v>10</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1052</v>
+        <v>1021</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>1038</v>
+        <v>1007</v>
       </c>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
@@ -5284,10 +5191,10 @@
         <v>11</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1053</v>
+        <v>1022</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>1054</v>
+        <v>1023</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
@@ -5308,10 +5215,10 @@
         <v>12</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1055</v>
+        <v>1024</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1040</v>
+        <v>1009</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
@@ -5330,7 +5237,7 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="32"/>
       <c r="B18" s="29" t="s">
-        <v>1056</v>
+        <v>1025</v>
       </c>
       <c r="C18" s="32"/>
       <c r="D18" s="32"/>
@@ -5347,7 +5254,7 @@
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="32"/>
       <c r="B19" s="29" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="C19" s="32"/>
       <c r="D19" s="32"/>
@@ -5357,7 +5264,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="35" t="s">
-        <v>1057</v>
+        <v>1026</v>
       </c>
       <c r="H19" s="35"/>
       <c r="I19" s="35"/>
@@ -5366,7 +5273,7 @@
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="32"/>
       <c r="B20" s="29" t="s">
-        <v>1058</v>
+        <v>1027</v>
       </c>
       <c r="C20" s="32"/>
       <c r="D20" s="32"/>
@@ -5376,7 +5283,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="35" t="s">
-        <v>1059</v>
+        <v>1028</v>
       </c>
       <c r="H20" s="35"/>
       <c r="I20" s="35"/>
@@ -5384,7 +5291,7 @@
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>1060</v>
+        <v>1029</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -5398,13 +5305,13 @@
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>1061</v>
+        <v>1030</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1033</v>
+        <v>1002</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>1062</v>
+        <v>1031</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -5416,13 +5323,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>1063</v>
+        <v>1032</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>1064</v>
+        <v>1033</v>
       </c>
       <c r="C24" s="48" t="s">
-        <v>1065</v>
+        <v>1034</v>
       </c>
       <c r="D24" s="48"/>
       <c r="E24" s="48"/>
@@ -5434,13 +5341,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>1066</v>
+        <v>1035</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>1067</v>
+        <v>1036</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>1068</v>
+        <v>1037</v>
       </c>
       <c r="D25" s="48"/>
       <c r="E25" s="48"/>
@@ -5452,13 +5359,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>1069</v>
+        <v>1038</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>1070</v>
+        <v>1039</v>
       </c>
       <c r="C26" s="48" t="s">
-        <v>1071</v>
+        <v>1040</v>
       </c>
       <c r="D26" s="48"/>
       <c r="E26" s="48"/>
@@ -5470,13 +5377,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>1072</v>
+        <v>1041</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>1073</v>
+        <v>1042</v>
       </c>
       <c r="C27" s="48" t="s">
-        <v>1074</v>
+        <v>1043</v>
       </c>
       <c r="D27" s="48"/>
       <c r="E27" s="48"/>
@@ -5533,7 +5440,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1075</v>
+        <v>1044</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5544,7 +5451,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1076</v>
+        <v>1045</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5555,7 +5462,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>1077</v>
+        <v>1046</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -5572,19 +5479,19 @@
         <v>42</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1078</v>
+        <v>1047</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>986</v>
+        <v>955</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>1079</v>
+        <v>1048</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5592,10 +5499,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1080</v>
+        <v>1049</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>1081</v>
+        <v>1050</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -5607,10 +5514,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1082</v>
+        <v>1051</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>1081</v>
+        <v>1050</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
@@ -5622,10 +5529,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1083</v>
+        <v>1052</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1081</v>
+        <v>1050</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
@@ -5637,10 +5544,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1084</v>
+        <v>1053</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1081</v>
+        <v>1050</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
@@ -5652,10 +5559,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1085</v>
+        <v>1054</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1086</v>
+        <v>1055</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
@@ -5667,10 +5574,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1087</v>
+        <v>1056</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>1086</v>
+        <v>1055</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
@@ -5682,10 +5589,10 @@
         <v>7</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1088</v>
+        <v>1057</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>1086</v>
+        <v>1055</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
@@ -5697,10 +5604,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1089</v>
+        <v>1058</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>1086</v>
+        <v>1055</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
@@ -5712,10 +5619,10 @@
         <v>9</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1090</v>
+        <v>1059</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>1086</v>
+        <v>1055</v>
       </c>
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
@@ -5727,10 +5634,10 @@
         <v>10</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1091</v>
+        <v>1060</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>1086</v>
+        <v>1055</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
@@ -5742,10 +5649,10 @@
         <v>11</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1092</v>
+        <v>1061</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>1093</v>
+        <v>1062</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
@@ -5757,10 +5664,10 @@
         <v>12</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1094</v>
+        <v>1063</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1093</v>
+        <v>1062</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
@@ -5772,10 +5679,10 @@
         <v>13</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1095</v>
+        <v>1064</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>1093</v>
+        <v>1062</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
@@ -5787,10 +5694,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1096</v>
+        <v>1065</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>1093</v>
+        <v>1062</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
@@ -5802,10 +5709,10 @@
         <v>15</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1097</v>
+        <v>1066</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>1093</v>
+        <v>1062</v>
       </c>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
@@ -5817,10 +5724,10 @@
         <v>16</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1098</v>
+        <v>1067</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>1099</v>
+        <v>1068</v>
       </c>
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
@@ -5832,10 +5739,10 @@
         <v>17</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1100</v>
+        <v>1069</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>1099</v>
+        <v>1068</v>
       </c>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
@@ -5847,10 +5754,10 @@
         <v>18</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1101</v>
+        <v>1070</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>1099</v>
+        <v>1068</v>
       </c>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
@@ -5862,10 +5769,10 @@
         <v>19</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1102</v>
+        <v>1071</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>1099</v>
+        <v>1068</v>
       </c>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
@@ -5877,10 +5784,10 @@
         <v>20</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>1103</v>
+        <v>1072</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>1104</v>
+        <v>1073</v>
       </c>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
@@ -5892,10 +5799,10 @@
         <v>21</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>1105</v>
+        <v>1074</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>1104</v>
+        <v>1073</v>
       </c>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
@@ -5907,10 +5814,10 @@
         <v>22</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>1106</v>
+        <v>1075</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>1104</v>
+        <v>1073</v>
       </c>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
@@ -5920,7 +5827,7 @@
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="32"/>
       <c r="B28" s="29" t="s">
-        <v>1107</v>
+        <v>1076</v>
       </c>
       <c r="C28" s="32"/>
       <c r="D28" s="30" t="n">
@@ -5930,13 +5837,13 @@
       <c r="E28" s="32"/>
       <c r="F28" s="32"/>
       <c r="G28" s="12" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="32"/>
       <c r="B29" s="29" t="s">
-        <v>1108</v>
+        <v>1077</v>
       </c>
       <c r="C29" s="32"/>
       <c r="D29" s="25" t="n">
@@ -5946,12 +5853,12 @@
       <c r="E29" s="32"/>
       <c r="F29" s="32"/>
       <c r="G29" s="12" t="s">
-        <v>1109</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>1110</v>
+        <v>1079</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -5963,54 +5870,54 @@
     <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="45"/>
       <c r="B33" s="10" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="C33" s="49" t="n">
-        <f aca="false">'7. Scorecard'!D17</f>
+        <f aca="false">'7. Scorecard'!D13</f>
         <v>0</v>
       </c>
       <c r="D33" s="49"/>
       <c r="E33" s="49"/>
       <c r="F33" s="49"/>
       <c r="G33" s="12" t="s">
-        <v>1111</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="45"/>
       <c r="B34" s="10" t="s">
-        <v>1112</v>
+        <v>1081</v>
       </c>
       <c r="C34" s="50" t="str">
-        <f aca="false">'7. Scorecard'!B18</f>
+        <f aca="false">'7. Scorecard'!B14</f>
         <v>Incompleto — pontue todos os critérios</v>
       </c>
       <c r="D34" s="50"/>
       <c r="E34" s="50"/>
       <c r="F34" s="50"/>
       <c r="G34" s="12" t="s">
-        <v>1111</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="45"/>
       <c r="B35" s="10" t="s">
-        <v>946</v>
+        <v>923</v>
       </c>
       <c r="C35" s="51" t="n">
         <f aca="false">'5. Custos'!B160</f>
@@ -6020,13 +5927,13 @@
       <c r="E35" s="51"/>
       <c r="F35" s="51"/>
       <c r="G35" s="12" t="s">
-        <v>1113</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="45"/>
       <c r="B36" s="10" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
       <c r="C36" s="50" t="str">
         <f aca="false">'5. Custos'!B177</f>
@@ -6036,13 +5943,13 @@
       <c r="E36" s="50"/>
       <c r="F36" s="50"/>
       <c r="G36" s="12" t="s">
-        <v>1113</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="45"/>
       <c r="B37" s="10" t="s">
-        <v>1114</v>
+        <v>1083</v>
       </c>
       <c r="C37" s="52" t="n">
         <f aca="false">'6. Viabilidade'!B33</f>
@@ -6052,13 +5959,13 @@
       <c r="E37" s="52"/>
       <c r="F37" s="52"/>
       <c r="G37" s="12" t="s">
-        <v>1115</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="45"/>
       <c r="B38" s="10" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="C38" s="52" t="n">
         <f aca="false">'6. Viabilidade'!B39</f>
@@ -6068,13 +5975,13 @@
       <c r="E38" s="52"/>
       <c r="F38" s="52"/>
       <c r="G38" s="12" t="s">
-        <v>1115</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="45"/>
       <c r="B39" s="10" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="C39" s="51" t="str">
         <f aca="false">'6. Viabilidade'!B40</f>
@@ -6084,13 +5991,13 @@
       <c r="E39" s="51"/>
       <c r="F39" s="51"/>
       <c r="G39" s="12" t="s">
-        <v>1115</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="45"/>
       <c r="B40" s="10" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="C40" s="49" t="str">
         <f aca="false">'6. Viabilidade'!B41</f>
@@ -6100,13 +6007,13 @@
       <c r="E40" s="49"/>
       <c r="F40" s="49"/>
       <c r="G40" s="12" t="s">
-        <v>1115</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="45"/>
       <c r="B41" s="10" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="C41" s="53" t="n">
         <f aca="false">'9. Riscos'!F19</f>
@@ -6116,13 +6023,13 @@
       <c r="E41" s="53"/>
       <c r="F41" s="53"/>
       <c r="G41" s="12" t="s">
-        <v>1116</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="45"/>
       <c r="B42" s="10" t="s">
-        <v>1117</v>
+        <v>1086</v>
       </c>
       <c r="C42" s="51" t="n">
         <f aca="false">D28</f>
@@ -6132,12 +6039,12 @@
       <c r="E42" s="51"/>
       <c r="F42" s="51"/>
       <c r="G42" s="12" t="s">
-        <v>1118</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>1119</v>
+        <v>1088</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -6152,130 +6059,130 @@
         <v>97</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>1120</v>
+        <v>1089</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="45"/>
       <c r="B46" s="10" t="s">
-        <v>1121</v>
+        <v>1090</v>
       </c>
       <c r="C46" s="34"/>
       <c r="D46" s="34"/>
       <c r="E46" s="34"/>
       <c r="F46" s="34"/>
       <c r="G46" s="12" t="s">
-        <v>1122</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="45"/>
       <c r="B47" s="10" t="s">
-        <v>1123</v>
+        <v>1092</v>
       </c>
       <c r="C47" s="34"/>
       <c r="D47" s="34"/>
       <c r="E47" s="34"/>
       <c r="F47" s="34"/>
       <c r="G47" s="12" t="s">
-        <v>1124</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="45"/>
       <c r="B48" s="10" t="s">
-        <v>1125</v>
+        <v>1094</v>
       </c>
       <c r="C48" s="34"/>
       <c r="D48" s="34"/>
       <c r="E48" s="34"/>
       <c r="F48" s="34"/>
       <c r="G48" s="12" t="s">
-        <v>1126</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="45"/>
       <c r="B49" s="10" t="s">
-        <v>1127</v>
+        <v>1096</v>
       </c>
       <c r="C49" s="34"/>
       <c r="D49" s="34"/>
       <c r="E49" s="34"/>
       <c r="F49" s="34"/>
       <c r="G49" s="12" t="s">
-        <v>1128</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="45"/>
       <c r="B50" s="10" t="s">
-        <v>1129</v>
+        <v>1098</v>
       </c>
       <c r="C50" s="34"/>
       <c r="D50" s="34"/>
       <c r="E50" s="34"/>
       <c r="F50" s="34"/>
       <c r="G50" s="12" t="s">
-        <v>1130</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="45"/>
       <c r="B51" s="10" t="s">
-        <v>1131</v>
+        <v>1100</v>
       </c>
       <c r="C51" s="34"/>
       <c r="D51" s="34"/>
       <c r="E51" s="34"/>
       <c r="F51" s="34"/>
       <c r="G51" s="12" t="s">
-        <v>1130</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="45"/>
       <c r="B52" s="10" t="s">
-        <v>1132</v>
+        <v>1101</v>
       </c>
       <c r="C52" s="34"/>
       <c r="D52" s="34"/>
       <c r="E52" s="34"/>
       <c r="F52" s="34"/>
       <c r="G52" s="12" t="s">
-        <v>1130</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="45"/>
       <c r="B53" s="10" t="s">
-        <v>1133</v>
+        <v>1102</v>
       </c>
       <c r="C53" s="34"/>
       <c r="D53" s="34"/>
       <c r="E53" s="34"/>
       <c r="F53" s="34"/>
       <c r="G53" s="12" t="s">
-        <v>1130</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="45"/>
       <c r="B54" s="10" t="s">
-        <v>1134</v>
+        <v>1103</v>
       </c>
       <c r="C54" s="34"/>
       <c r="D54" s="34"/>
       <c r="E54" s="34"/>
       <c r="F54" s="34"/>
       <c r="G54" s="12" t="s">
-        <v>1130</v>
+        <v>1099</v>
       </c>
     </row>
   </sheetData>
@@ -6331,7 +6238,7 @@
     <tabColor rgb="FFEC008C"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C107"/>
+  <dimension ref="A1:C93"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -6443,40 +6350,40 @@
         <v>115</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="12" t="s">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
+      <c r="B17" s="11"/>
+      <c r="C17" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="12" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="B18" s="11"/>
+      <c r="C18" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6497,56 +6404,56 @@
         <v>124</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="12" t="s">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
+      <c r="B24" s="11"/>
+      <c r="C24" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="12" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
+      <c r="B25" s="14"/>
+      <c r="C25" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="12" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+      <c r="B26" s="15"/>
+      <c r="C26" s="12" t="s">
         <v>131</v>
-      </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B27" s="11"/>
+      <c r="B27" s="16"/>
       <c r="C27" s="12" t="s">
         <v>133</v>
       </c>
@@ -6569,40 +6476,40 @@
         <v>137</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="s">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="12" t="s">
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="10" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10" t="s">
+      <c r="B33" s="11"/>
+      <c r="C33" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="12" t="s">
+    </row>
+    <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="10" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
+      <c r="B34" s="11"/>
+      <c r="C34" s="12" t="s">
         <v>142</v>
-      </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-    </row>
-    <row r="34" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6632,49 +6539,49 @@
         <v>148</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="10" t="s">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B38" s="11"/>
-      <c r="C38" s="12" t="s">
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+    </row>
+    <row r="40" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="10" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10" t="s">
+      <c r="B41" s="11"/>
+      <c r="C41" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="12" t="s">
+    </row>
+    <row r="42" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="10" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="10" t="s">
+      <c r="B42" s="11"/>
+      <c r="C42" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="B40" s="11"/>
-      <c r="C40" s="12" t="s">
+    </row>
+    <row r="43" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="10" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
+      <c r="B43" s="11"/>
+      <c r="C43" s="12" t="s">
         <v>155</v>
-      </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-    </row>
-    <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6731,58 +6638,58 @@
         <v>167</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="10" t="s">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B50" s="11"/>
-      <c r="C50" s="12" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="B52" s="11"/>
-      <c r="C52" s="12" t="s">
-        <v>173</v>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+    </row>
+    <row r="52" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B53" s="11"/>
       <c r="C53" s="12" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B54" s="11"/>
+      <c r="C54" s="12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B55" s="11"/>
+      <c r="C55" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="10" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="s">
+      <c r="B56" s="11"/>
+      <c r="C56" s="12" t="s">
         <v>176</v>
-      </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-    </row>
-    <row r="56" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6794,192 +6701,243 @@
         <v>178</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="10" t="s">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B58" s="11"/>
-      <c r="C58" s="12" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="B59" s="11"/>
-      <c r="C59" s="12" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="B60" s="11"/>
-      <c r="C60" s="12" t="s">
-        <v>184</v>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+    </row>
+    <row r="60" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B61" s="11"/>
       <c r="C61" s="12" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="10" t="s">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="B62" s="11"/>
       <c r="C62" s="12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B63" s="11"/>
+      <c r="C63" s="12" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="B64" s="13"/>
+      <c r="C64" s="12" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="3" t="s">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-    </row>
-    <row r="65" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="10" t="s">
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+    </row>
+    <row r="67" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="B66" s="11"/>
-      <c r="C66" s="12" t="s">
+      <c r="B67" s="4" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="67" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="10" t="s">
+      <c r="C67" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B67" s="15"/>
-      <c r="C67" s="12" t="s">
+    </row>
+    <row r="68" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="10" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="68" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="10" t="s">
+      <c r="B68" s="17" t="n">
+        <f aca="false">'2. Mercado'!B16</f>
+        <v>0</v>
+      </c>
+      <c r="C68" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="B68" s="11"/>
-      <c r="C68" s="12" t="s">
+    </row>
+    <row r="69" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="10" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="69" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="10" t="s">
+      <c r="B69" s="18" t="n">
+        <f aca="false">'5. Custos'!B166</f>
+        <v>0</v>
+      </c>
+      <c r="C69" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="B69" s="11"/>
-      <c r="C69" s="12" t="s">
+    </row>
+    <row r="70" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="10" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="70" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="10" t="s">
+      <c r="B70" s="18" t="n">
+        <f aca="false">'5. Custos'!B123</f>
+        <v>0</v>
+      </c>
+      <c r="C70" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="B70" s="11"/>
-      <c r="C70" s="12" t="s">
+    </row>
+    <row r="71" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="10" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="71" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="10" t="s">
+      <c r="B71" s="19" t="n">
+        <f aca="false">'5. Custos'!C118</f>
+        <v>0</v>
+      </c>
+      <c r="C71" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="B71" s="11"/>
-      <c r="C71" s="12" t="s">
+    </row>
+    <row r="72" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="10" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3" t="s">
+      <c r="B72" s="19" t="n">
+        <f aca="false">'5. Custos'!C119</f>
+        <v>0</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-    </row>
-    <row r="74" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B73" s="19" t="n">
+        <f aca="false">'5. Custos'!C120</f>
+        <v>0</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="B74" s="19" t="n">
+        <f aca="false">'5. Custos'!C121</f>
+        <v>0</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="B75" s="11"/>
+        <v>203</v>
+      </c>
+      <c r="B75" s="19" t="n">
+        <f aca="false">'5. Custos'!C122</f>
+        <v>0</v>
+      </c>
       <c r="C75" s="12" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="B76" s="11"/>
+      <c r="B76" s="18" t="n">
+        <f aca="false">'5. Custos'!B129</f>
+        <v>0</v>
+      </c>
       <c r="C76" s="12" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="B77" s="11"/>
+      <c r="B77" s="18" t="n">
+        <f aca="false">'5. Custos'!B140</f>
+        <v>0</v>
+      </c>
       <c r="C77" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="10" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="78" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="10" t="s">
+      <c r="B78" s="19" t="n">
+        <f aca="false">'5. Custos'!B151</f>
+        <v>0</v>
+      </c>
+      <c r="C78" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="B78" s="13"/>
-      <c r="C78" s="12" t="s">
+    </row>
+    <row r="79" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="10" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="3" t="s">
+      <c r="B79" s="19" t="n">
+        <f aca="false">'5. Custos'!B160</f>
+        <v>0</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="B80" s="3"/>
-      <c r="C80" s="3"/>
-    </row>
-    <row r="81" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="4" t="s">
+      <c r="B80" s="20" t="str">
+        <f aca="false">'5. Custos'!B177</f>
+        <v>Preencha as premissas</v>
+      </c>
+      <c r="C80" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="B81" s="4" t="s">
+    </row>
+    <row r="81" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="B81" s="21" t="n">
+        <f aca="false">'5. Custos'!B184</f>
+        <v>0</v>
+      </c>
+      <c r="C81" s="12" t="s">
         <v>213</v>
       </c>
     </row>
@@ -6988,8 +6946,8 @@
         <v>214</v>
       </c>
       <c r="B82" s="17" t="n">
-        <f aca="false">'2. Mercado'!B16</f>
-        <v>0</v>
+        <f aca="false">'6. Viabilidade'!B33</f>
+        <v>5114</v>
       </c>
       <c r="C82" s="12" t="s">
         <v>215</v>
@@ -6999,9 +6957,9 @@
       <c r="A83" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="B83" s="18" t="n">
-        <f aca="false">'5. Custos'!B166</f>
-        <v>0</v>
+      <c r="B83" s="17" t="n">
+        <f aca="false">'6. Viabilidade'!B39</f>
+        <v>-5114</v>
       </c>
       <c r="C83" s="12" t="s">
         <v>217</v>
@@ -7011,32 +6969,32 @@
       <c r="A84" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="B84" s="18" t="n">
-        <f aca="false">'5. Custos'!B123</f>
-        <v>0</v>
+      <c r="B84" s="19" t="str">
+        <f aca="false">'6. Viabilidade'!B40</f>
+        <v>n/d</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="B85" s="19" t="n">
-        <f aca="false">'5. Custos'!C118</f>
-        <v>0</v>
+        <v>219</v>
+      </c>
+      <c r="B85" s="22" t="str">
+        <f aca="false">'6. Viabilidade'!B41</f>
+        <v>Acima de 3 anos</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="B86" s="19" t="n">
-        <f aca="false">'5. Custos'!C119</f>
+        <v>220</v>
+      </c>
+      <c r="B86" s="22" t="n">
+        <f aca="false">'7. Scorecard'!D13</f>
         <v>0</v>
       </c>
       <c r="C86" s="12" t="s">
@@ -7045,11 +7003,11 @@
     </row>
     <row r="87" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="B87" s="19" t="n">
-        <f aca="false">'5. Custos'!C120</f>
-        <v>0</v>
+        <v>222</v>
+      </c>
+      <c r="B87" s="20" t="str">
+        <f aca="false">'7. Scorecard'!B14</f>
+        <v>Incompleto — pontue todos os critérios</v>
       </c>
       <c r="C87" s="12" t="s">
         <v>221</v>
@@ -7057,34 +7015,34 @@
     </row>
     <row r="88" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="B88" s="22" t="n">
+        <f aca="false">'8. Cronograma'!E27</f>
+        <v>18.8333333333333</v>
+      </c>
+      <c r="C88" s="12" t="s">
         <v>224</v>
-      </c>
-      <c r="B88" s="19" t="n">
-        <f aca="false">'5. Custos'!C121</f>
-        <v>0</v>
-      </c>
-      <c r="C88" s="12" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="B89" s="19" t="n">
-        <f aca="false">'5. Custos'!C122</f>
-        <v>0</v>
+      <c r="B89" s="23" t="str">
+        <f aca="false">'8. Cronograma'!F28</f>
+        <v/>
       </c>
       <c r="C89" s="12" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="B90" s="18" t="n">
-        <f aca="false">'5. Custos'!B129</f>
+      <c r="B90" s="21" t="n">
+        <f aca="false">'9. Riscos'!F19</f>
         <v>0</v>
       </c>
       <c r="C90" s="12" t="s">
@@ -7095,203 +7053,34 @@
       <c r="A91" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B91" s="18" t="n">
-        <f aca="false">'5. Custos'!B140</f>
+      <c r="B91" s="19" t="n">
+        <f aca="false">'10. Aprovação'!D28</f>
         <v>0</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="B92" s="19" t="n">
-        <f aca="false">'5. Custos'!B151</f>
-        <v>0</v>
-      </c>
-      <c r="C92" s="12" t="s">
+    </row>
+    <row r="93" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="24" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="93" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="B93" s="19" t="n">
-        <f aca="false">'5. Custos'!B160</f>
-        <v>0</v>
-      </c>
-      <c r="C93" s="12" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="B94" s="20" t="str">
-        <f aca="false">'5. Custos'!B177</f>
-        <v>Preencha as premissas</v>
-      </c>
-      <c r="C94" s="12" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="B95" s="21" t="n">
-        <f aca="false">'5. Custos'!B184</f>
-        <v>0</v>
-      </c>
-      <c r="C95" s="12" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="B96" s="17" t="n">
-        <f aca="false">'6. Viabilidade'!B33</f>
-        <v>5114</v>
-      </c>
-      <c r="C96" s="12" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="B97" s="17" t="n">
-        <f aca="false">'6. Viabilidade'!B39</f>
-        <v>-5114</v>
-      </c>
-      <c r="C97" s="12" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="B98" s="19" t="str">
-        <f aca="false">'6. Viabilidade'!B40</f>
-        <v>n/d</v>
-      </c>
-      <c r="C98" s="12" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="B99" s="22" t="str">
-        <f aca="false">'6. Viabilidade'!B41</f>
-        <v>Acima de 3 anos</v>
-      </c>
-      <c r="C99" s="12" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="B100" s="22" t="n">
-        <f aca="false">'7. Scorecard'!D17</f>
-        <v>0</v>
-      </c>
-      <c r="C100" s="12" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="B101" s="20" t="str">
-        <f aca="false">'7. Scorecard'!B18</f>
-        <v>Incompleto — pontue todos os critérios</v>
-      </c>
-      <c r="C101" s="12" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="B102" s="22" t="n">
-        <f aca="false">'8. Cronograma'!E27</f>
-        <v>18.8333333333333</v>
-      </c>
-      <c r="C102" s="12" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="B103" s="23" t="str">
-        <f aca="false">'8. Cronograma'!F28</f>
-        <v/>
-      </c>
-      <c r="C103" s="12" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="B104" s="21" t="n">
-        <f aca="false">'9. Riscos'!F19</f>
-        <v>0</v>
-      </c>
-      <c r="C104" s="12" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="B105" s="19" t="n">
-        <f aca="false">'10. Aprovação'!D28</f>
-        <v>0</v>
-      </c>
-      <c r="C105" s="12" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="B107" s="24"/>
-      <c r="C107" s="24"/>
+      <c r="B93" s="24"/>
+      <c r="C93" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A73:C73"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="A93:C93"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7322,7 +7111,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7335,7 +7124,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7348,7 +7137,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -7356,213 +7145,213 @@
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="B6" s="14"/>
       <c r="C6" s="12" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>261</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="12" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="B8" s="25" t="n">
         <f aca="false">IFERROR(B6*B7,0)</f>
         <v>0</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="B9" s="26"/>
       <c r="C9" s="12" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="B10" s="25" t="n">
         <f aca="false">IFERROR(B8*B9,0)</f>
         <v>0</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="B11" s="27"/>
       <c r="C11" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>274</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="B12" s="28" t="n">
         <f aca="false">IFERROR(B10*B11,0)</f>
         <v>0</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>277</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="12" t="s">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="B14" s="28" t="n">
         <f aca="false">IFERROR(B12*B13,0)</f>
         <v>0</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>282</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>283</v>
+        <v>261</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="B16" s="28" t="n">
         <f aca="false">IFERROR(B14*B15,0)</f>
         <v>0</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="B17" s="25" t="n">
         <f aca="false">IFERROR(B16/B11,0)</f>
         <v>0</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>288</v>
+        <v>266</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="29" t="s">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="B19" s="21" t="n">
-        <f aca="false">'1. Briefing'!B28</f>
+        <f aca="false">'1. Briefing'!B25</f>
         <v>0</v>
       </c>
       <c r="C19" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>268</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="29" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="B20" s="30" t="str">
         <f aca="false">IF(B17=0,"",IFERROR(B19/B17-1,""))</f>
         <v/>
       </c>
       <c r="C20" s="12" t="s">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>293</v>
+        <v>271</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>294</v>
+        <v>272</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -7575,39 +7364,39 @@
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>295</v>
+        <v>104</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="C24" s="26" t="n">
         <v>200</v>
@@ -7620,16 +7409,16 @@
         <v>9.45</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7788,7 +7577,7 @@
     </row>
     <row r="36" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="29" t="s">
-        <v>310</v>
+        <v>287</v>
       </c>
       <c r="B36" s="32"/>
       <c r="C36" s="33" t="n">
@@ -7804,12 +7593,12 @@
         <v>9.45</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="29" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="B37" s="32"/>
       <c r="C37" s="32"/>
@@ -7819,12 +7608,12 @@
         <v>9.45</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="29" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="B38" s="32"/>
       <c r="C38" s="32"/>
@@ -7834,12 +7623,12 @@
         <v>9.45</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="29" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="B39" s="25" t="n">
         <f aca="false">COUNT(D24:D35)</f>
@@ -7849,12 +7638,12 @@
       <c r="D39" s="32"/>
       <c r="E39" s="32"/>
       <c r="F39" s="12" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -7867,7 +7656,7 @@
     </row>
     <row r="42" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>98</v>
@@ -7882,7 +7671,7 @@
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>320</v>
+        <v>297</v>
       </c>
       <c r="B43" s="34"/>
       <c r="C43" s="34"/>
@@ -7895,7 +7684,7 @@
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="B44" s="34"/>
       <c r="C44" s="34"/>
@@ -7908,7 +7697,7 @@
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="B45" s="34"/>
       <c r="C45" s="34"/>
@@ -7921,7 +7710,7 @@
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="B46" s="34"/>
       <c r="C46" s="34"/>
@@ -7934,7 +7723,7 @@
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="B47" s="34"/>
       <c r="C47" s="34"/>
@@ -7986,7 +7775,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7997,7 +7786,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8008,7 +7797,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -8016,131 +7805,131 @@
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>329</v>
+        <v>306</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>332</v>
+        <v>309</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
       <c r="D6" s="12" t="s">
-        <v>333</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>334</v>
+        <v>311</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="12" t="s">
-        <v>335</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>336</v>
+        <v>313</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
       <c r="D8" s="12" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
       <c r="D9" s="12" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>340</v>
+        <v>317</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
       <c r="D10" s="12" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
       <c r="D11" s="12" t="s">
-        <v>343</v>
+        <v>320</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="12" t="s">
-        <v>345</v>
+        <v>322</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
       <c r="D13" s="12" t="s">
-        <v>347</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
       <c r="D14" s="12" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
       <c r="D15" s="12" t="s">
-        <v>351</v>
+        <v>328</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>352</v>
+        <v>329</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
       <c r="D16" s="12" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>354</v>
+        <v>331</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -8154,228 +7943,228 @@
         <v>42</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>357</v>
+        <v>334</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="D20" s="13"/>
       <c r="E20" s="12" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="F20" s="27"/>
       <c r="G20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
       <c r="D21" s="13"/>
       <c r="E21" s="12" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="F21" s="27"/>
       <c r="G21" s="11"/>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="13"/>
       <c r="E22" s="12" t="s">
-        <v>365</v>
+        <v>342</v>
       </c>
       <c r="F22" s="27"/>
       <c r="G22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>366</v>
+        <v>343</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="13"/>
       <c r="E23" s="12" t="s">
-        <v>367</v>
+        <v>344</v>
       </c>
       <c r="F23" s="27"/>
       <c r="G23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>368</v>
+        <v>345</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="D24" s="13"/>
       <c r="E24" s="12" t="s">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="F24" s="27"/>
       <c r="G24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="13"/>
       <c r="E25" s="12" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
       <c r="F25" s="27"/>
       <c r="G25" s="11"/>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="13"/>
       <c r="E26" s="12" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="F26" s="27"/>
       <c r="G26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>374</v>
+        <v>351</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="13"/>
       <c r="E27" s="12" t="s">
-        <v>375</v>
+        <v>352</v>
       </c>
       <c r="F27" s="27"/>
       <c r="G27" s="11"/>
     </row>
     <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>376</v>
+        <v>353</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="D28" s="13"/>
       <c r="E28" s="12" t="s">
-        <v>377</v>
+        <v>354</v>
       </c>
       <c r="F28" s="27"/>
       <c r="G28" s="11"/>
     </row>
     <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>378</v>
+        <v>355</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
       <c r="D29" s="13"/>
       <c r="E29" s="12" t="s">
-        <v>379</v>
+        <v>356</v>
       </c>
       <c r="F29" s="27"/>
       <c r="G29" s="11"/>
     </row>
     <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>380</v>
+        <v>357</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
       <c r="D30" s="13"/>
       <c r="E30" s="12" t="s">
-        <v>381</v>
+        <v>358</v>
       </c>
       <c r="F30" s="27"/>
       <c r="G30" s="11"/>
     </row>
     <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>382</v>
+        <v>359</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="13"/>
       <c r="E31" s="12" t="s">
-        <v>383</v>
+        <v>360</v>
       </c>
       <c r="F31" s="27"/>
       <c r="G31" s="11"/>
     </row>
     <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>384</v>
+        <v>361</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
       <c r="D32" s="13"/>
       <c r="E32" s="12" t="s">
-        <v>385</v>
+        <v>362</v>
       </c>
       <c r="F32" s="27"/>
       <c r="G32" s="11"/>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="D33" s="13"/>
       <c r="E33" s="12" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
       <c r="F33" s="27"/>
       <c r="G33" s="11"/>
     </row>
     <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>388</v>
+        <v>365</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="D34" s="13"/>
       <c r="E34" s="12" t="s">
-        <v>389</v>
+        <v>366</v>
       </c>
       <c r="F34" s="27"/>
       <c r="G34" s="11"/>
     </row>
     <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="29" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="B35" s="32"/>
       <c r="C35" s="32"/>
       <c r="D35" s="32"/>
       <c r="E35" s="12" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="F35" s="28" t="n">
         <f aca="false">SUM(F20:F34)</f>
@@ -8385,7 +8174,7 @@
     </row>
     <row r="36" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="29" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="B36" s="30" t="n">
         <f aca="false">IFERROR(COUNTIF(G20:G34,"Sim")/(COUNTA(G20:G34)-COUNTIF(G20:G34,"N/A")),0)</f>
@@ -8394,14 +8183,14 @@
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="E36" s="12" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="F36" s="32"/>
       <c r="G36" s="32"/>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -8412,22 +8201,22 @@
     </row>
     <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="G39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>396</v>
+        <v>373</v>
       </c>
       <c r="B40" s="14" t="n">
         <v>1</v>
@@ -8436,36 +8225,36 @@
       <c r="D40" s="32"/>
       <c r="E40" s="32"/>
       <c r="F40" s="35" t="s">
-        <v>397</v>
+        <v>374</v>
       </c>
       <c r="G40" s="35"/>
     </row>
     <row r="42" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>399</v>
+        <v>376</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>402</v>
+        <v>379</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>403</v>
+        <v>380</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>404</v>
+        <v>381</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>405</v>
+        <v>382</v>
       </c>
       <c r="B43" s="25" t="n">
         <f aca="false">$B$40</f>
@@ -8482,15 +8271,15 @@
         <v>30</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>406</v>
+        <v>383</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>407</v>
+        <v>384</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>408</v>
+        <v>385</v>
       </c>
       <c r="B44" s="25" t="n">
         <f aca="false">$B$40</f>
@@ -8505,15 +8294,15 @@
       </c>
       <c r="E44" s="14"/>
       <c r="F44" s="12" t="s">
-        <v>409</v>
+        <v>386</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>410</v>
+        <v>387</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>411</v>
+        <v>388</v>
       </c>
       <c r="B45" s="25" t="n">
         <f aca="false">$B$40</f>
@@ -8528,15 +8317,15 @@
       </c>
       <c r="E45" s="14"/>
       <c r="F45" s="12" t="s">
-        <v>412</v>
+        <v>389</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>410</v>
+        <v>387</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>413</v>
+        <v>390</v>
       </c>
       <c r="B46" s="25" t="n">
         <f aca="false">$B$40</f>
@@ -8551,15 +8340,15 @@
       </c>
       <c r="E46" s="14"/>
       <c r="F46" s="12" t="s">
-        <v>414</v>
+        <v>391</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>410</v>
+        <v>387</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="29" t="s">
-        <v>415</v>
+        <v>392</v>
       </c>
       <c r="B47" s="25" t="n">
         <f aca="false">$B$40</f>
@@ -8575,15 +8364,15 @@
         <v>30</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>416</v>
+        <v>393</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>417</v>
+        <v>394</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="29" t="s">
-        <v>418</v>
+        <v>395</v>
       </c>
       <c r="B48" s="32"/>
       <c r="C48" s="31" t="n">
@@ -8596,15 +8385,15 @@
         <v>30</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>419</v>
+        <v>396</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>420</v>
+        <v>397</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="29" t="s">
-        <v>421</v>
+        <v>398</v>
       </c>
       <c r="B49" s="36" t="str">
         <f aca="false">IF(COUNTBLANK(E43:E46)=0,"Todos os prazos informados","Faltam "&amp;COUNTBLANK(E43:E46)&amp;" prazo(s) de teste básico — confirmar com o laboratório antes de fechar o cronograma da aba 8")</f>
@@ -8618,7 +8407,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="37" t="s">
-        <v>422</v>
+        <v>399</v>
       </c>
       <c r="B50" s="37"/>
       <c r="C50" s="37"/>
@@ -8638,7 +8427,7 @@
     </row>
     <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>423</v>
+        <v>400</v>
       </c>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -8649,33 +8438,33 @@
     </row>
     <row r="54" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>424</v>
+        <v>401</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>402</v>
+        <v>379</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>403</v>
+        <v>380</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>427</v>
+        <v>404</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
-        <v>428</v>
+        <v>405</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>429</v>
+        <v>406</v>
       </c>
       <c r="C55" s="27"/>
       <c r="D55" s="31" t="str">
@@ -8684,16 +8473,16 @@
       </c>
       <c r="E55" s="14"/>
       <c r="F55" s="12" t="s">
-        <v>430</v>
+        <v>407</v>
       </c>
       <c r="G55" s="11"/>
     </row>
     <row r="56" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
-        <v>431</v>
+        <v>408</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>429</v>
+        <v>406</v>
       </c>
       <c r="C56" s="27"/>
       <c r="D56" s="31" t="str">
@@ -8702,16 +8491,16 @@
       </c>
       <c r="E56" s="14"/>
       <c r="F56" s="12" t="s">
-        <v>432</v>
+        <v>409</v>
       </c>
       <c r="G56" s="11"/>
     </row>
     <row r="57" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
-        <v>433</v>
+        <v>410</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>429</v>
+        <v>406</v>
       </c>
       <c r="C57" s="27"/>
       <c r="D57" s="31" t="str">
@@ -8720,16 +8509,16 @@
       </c>
       <c r="E57" s="14"/>
       <c r="F57" s="12" t="s">
-        <v>434</v>
+        <v>411</v>
       </c>
       <c r="G57" s="11"/>
     </row>
     <row r="58" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
-        <v>378</v>
+        <v>355</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>429</v>
+        <v>406</v>
       </c>
       <c r="C58" s="27"/>
       <c r="D58" s="31" t="str">
@@ -8738,16 +8527,16 @@
       </c>
       <c r="E58" s="14"/>
       <c r="F58" s="12" t="s">
-        <v>435</v>
+        <v>412</v>
       </c>
       <c r="G58" s="11"/>
     </row>
     <row r="59" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
-        <v>436</v>
+        <v>413</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>437</v>
+        <v>414</v>
       </c>
       <c r="C59" s="27"/>
       <c r="D59" s="31" t="str">
@@ -8756,16 +8545,16 @@
       </c>
       <c r="E59" s="14"/>
       <c r="F59" s="12" t="s">
-        <v>438</v>
+        <v>415</v>
       </c>
       <c r="G59" s="11"/>
     </row>
     <row r="60" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
-        <v>439</v>
+        <v>416</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>440</v>
+        <v>417</v>
       </c>
       <c r="C60" s="27"/>
       <c r="D60" s="31" t="str">
@@ -8774,16 +8563,16 @@
       </c>
       <c r="E60" s="14"/>
       <c r="F60" s="12" t="s">
-        <v>441</v>
+        <v>418</v>
       </c>
       <c r="G60" s="11"/>
     </row>
     <row r="61" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="s">
-        <v>442</v>
+        <v>419</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>443</v>
+        <v>420</v>
       </c>
       <c r="C61" s="27"/>
       <c r="D61" s="31" t="str">
@@ -8792,16 +8581,16 @@
       </c>
       <c r="E61" s="14"/>
       <c r="F61" s="12" t="s">
-        <v>444</v>
+        <v>421</v>
       </c>
       <c r="G61" s="11"/>
     </row>
     <row r="62" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="10" t="s">
-        <v>445</v>
+        <v>422</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>446</v>
+        <v>423</v>
       </c>
       <c r="C62" s="27"/>
       <c r="D62" s="31" t="str">
@@ -8810,16 +8599,16 @@
       </c>
       <c r="E62" s="14"/>
       <c r="F62" s="12" t="s">
-        <v>447</v>
+        <v>424</v>
       </c>
       <c r="G62" s="11"/>
     </row>
     <row r="63" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="s">
-        <v>448</v>
+        <v>425</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>449</v>
+        <v>426</v>
       </c>
       <c r="C63" s="27"/>
       <c r="D63" s="31" t="str">
@@ -8828,16 +8617,16 @@
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="12" t="s">
-        <v>450</v>
+        <v>427</v>
       </c>
       <c r="G63" s="11"/>
     </row>
     <row r="64" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="s">
-        <v>451</v>
+        <v>428</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>452</v>
+        <v>429</v>
       </c>
       <c r="C64" s="27"/>
       <c r="D64" s="31" t="str">
@@ -8846,16 +8635,16 @@
       </c>
       <c r="E64" s="14"/>
       <c r="F64" s="12" t="s">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="G64" s="11"/>
     </row>
     <row r="65" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="10" t="s">
-        <v>454</v>
+        <v>431</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>429</v>
+        <v>406</v>
       </c>
       <c r="C65" s="27"/>
       <c r="D65" s="31" t="str">
@@ -8864,16 +8653,16 @@
       </c>
       <c r="E65" s="14"/>
       <c r="F65" s="12" t="s">
-        <v>455</v>
+        <v>432</v>
       </c>
       <c r="G65" s="11"/>
     </row>
     <row r="66" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="s">
-        <v>456</v>
+        <v>433</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>429</v>
+        <v>406</v>
       </c>
       <c r="C66" s="27"/>
       <c r="D66" s="31" t="str">
@@ -8882,16 +8671,16 @@
       </c>
       <c r="E66" s="14"/>
       <c r="F66" s="12" t="s">
-        <v>457</v>
+        <v>434</v>
       </c>
       <c r="G66" s="11"/>
     </row>
     <row r="67" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="10" t="s">
-        <v>458</v>
+        <v>435</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>429</v>
+        <v>406</v>
       </c>
       <c r="C67" s="27"/>
       <c r="D67" s="31" t="str">
@@ -8900,16 +8689,16 @@
       </c>
       <c r="E67" s="14"/>
       <c r="F67" s="12" t="s">
-        <v>459</v>
+        <v>436</v>
       </c>
       <c r="G67" s="11"/>
     </row>
     <row r="68" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="10" t="s">
-        <v>460</v>
+        <v>437</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>429</v>
+        <v>406</v>
       </c>
       <c r="C68" s="27"/>
       <c r="D68" s="31" t="str">
@@ -8918,7 +8707,7 @@
       </c>
       <c r="E68" s="14"/>
       <c r="F68" s="12" t="s">
-        <v>461</v>
+        <v>438</v>
       </c>
       <c r="G68" s="11"/>
     </row>
@@ -8960,7 +8749,7 @@
     </row>
     <row r="72" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="29" t="s">
-        <v>462</v>
+        <v>439</v>
       </c>
       <c r="B72" s="32"/>
       <c r="C72" s="31" t="n">
@@ -8976,13 +8765,13 @@
         <v>0</v>
       </c>
       <c r="F72" s="12" t="s">
-        <v>463</v>
+        <v>440</v>
       </c>
       <c r="G72" s="32"/>
     </row>
     <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
-        <v>464</v>
+        <v>441</v>
       </c>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -8993,22 +8782,22 @@
     </row>
     <row r="75" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="s">
-        <v>465</v>
+        <v>442</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
       <c r="F75" s="4" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="G75" s="4"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="38" t="s">
-        <v>466</v>
+        <v>443</v>
       </c>
       <c r="B76" s="28" t="n">
         <f aca="false">D47+D72</f>
@@ -9018,13 +8807,13 @@
       <c r="D76" s="32"/>
       <c r="E76" s="32"/>
       <c r="F76" s="35" t="s">
-        <v>467</v>
+        <v>444</v>
       </c>
       <c r="G76" s="35"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="s">
-        <v>468</v>
+        <v>445</v>
       </c>
       <c r="B77" s="25" t="n">
         <f aca="false">E47+E72</f>
@@ -9034,13 +8823,13 @@
       <c r="D77" s="32"/>
       <c r="E77" s="32"/>
       <c r="F77" s="35" t="s">
-        <v>469</v>
+        <v>446</v>
       </c>
       <c r="G77" s="35"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="s">
-        <v>470</v>
+        <v>447</v>
       </c>
       <c r="B78" s="25" t="n">
         <f aca="false">MAX(E48,E72)</f>
@@ -9050,13 +8839,13 @@
       <c r="D78" s="32"/>
       <c r="E78" s="32"/>
       <c r="F78" s="35" t="s">
-        <v>471</v>
+        <v>448</v>
       </c>
       <c r="G78" s="35"/>
     </row>
     <row r="79" customFormat="false" ht="19.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="10" t="s">
-        <v>472</v>
+        <v>449</v>
       </c>
       <c r="B79" s="31" t="n">
         <f aca="false">C48+C72</f>
@@ -9066,7 +8855,7 @@
       <c r="D79" s="32"/>
       <c r="E79" s="32"/>
       <c r="F79" s="35" t="s">
-        <v>473</v>
+        <v>450</v>
       </c>
       <c r="G79" s="35"/>
     </row>
@@ -9129,7 +8918,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>474</v>
+        <v>451</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9142,7 +8931,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>475</v>
+        <v>452</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -9155,7 +8944,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>476</v>
+        <v>453</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -9168,7 +8957,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="35" t="s">
-        <v>477</v>
+        <v>454</v>
       </c>
       <c r="B5" s="35"/>
       <c r="C5" s="35"/>
@@ -9181,40 +8970,40 @@
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>478</v>
+        <v>455</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>479</v>
+        <v>456</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>480</v>
+        <v>457</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>481</v>
+        <v>458</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>483</v>
+        <v>460</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>484</v>
+        <v>461</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>485</v>
+        <v>462</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>486</v>
+        <v>463</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>487</v>
+        <v>464</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11" t="s">
-        <v>488</v>
+        <v>465</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="14"/>
@@ -9225,11 +9014,11 @@
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11" t="s">
-        <v>490</v>
+        <v>467</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="14"/>
@@ -9240,11 +9029,11 @@
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>491</v>
+        <v>468</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11" t="s">
-        <v>492</v>
+        <v>469</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="14"/>
@@ -9255,11 +9044,11 @@
     </row>
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11" t="s">
-        <v>494</v>
+        <v>471</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="14"/>
@@ -9270,11 +9059,11 @@
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>495</v>
+        <v>472</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11" t="s">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="14"/>
@@ -9285,11 +9074,11 @@
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>497</v>
+        <v>474</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11" t="s">
-        <v>498</v>
+        <v>475</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="14"/>
@@ -9300,11 +9089,11 @@
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>499</v>
+        <v>476</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11" t="s">
-        <v>500</v>
+        <v>477</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="14"/>
@@ -9315,11 +9104,11 @@
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>501</v>
+        <v>478</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11" t="s">
-        <v>502</v>
+        <v>479</v>
       </c>
       <c r="D14" s="11"/>
       <c r="E14" s="14"/>
@@ -9330,7 +9119,7 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="29" t="s">
-        <v>503</v>
+        <v>480</v>
       </c>
       <c r="B15" s="32"/>
       <c r="C15" s="32"/>
@@ -9349,7 +9138,7 @@
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="29" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="B16" s="32"/>
       <c r="C16" s="32"/>
@@ -9365,7 +9154,7 @@
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="29" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="B17" s="32"/>
       <c r="C17" s="32"/>
@@ -9381,7 +9170,7 @@
     </row>
     <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="29" t="s">
-        <v>506</v>
+        <v>483</v>
       </c>
       <c r="B18" s="32"/>
       <c r="C18" s="32"/>
@@ -9393,13 +9182,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>507</v>
+        <v>484</v>
       </c>
       <c r="I18" s="32"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>508</v>
+        <v>485</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -9412,16 +9201,16 @@
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>509</v>
+        <v>486</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>510</v>
+        <v>487</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -9431,7 +9220,7 @@
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -9444,7 +9233,7 @@
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>513</v>
+        <v>490</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -9457,7 +9246,7 @@
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>514</v>
+        <v>491</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -9470,7 +9259,7 @@
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>515</v>
+        <v>492</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -9483,7 +9272,7 @@
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>516</v>
+        <v>493</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -9496,7 +9285,7 @@
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>517</v>
+        <v>494</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -9509,7 +9298,7 @@
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>518</v>
+        <v>495</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -9522,7 +9311,7 @@
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>519</v>
+        <v>496</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -9535,7 +9324,7 @@
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>520</v>
+        <v>497</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -9548,7 +9337,7 @@
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>521</v>
+        <v>498</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -9561,7 +9350,7 @@
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>522</v>
+        <v>499</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -9574,7 +9363,7 @@
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>523</v>
+        <v>500</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -9587,7 +9376,7 @@
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>524</v>
+        <v>501</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -9600,7 +9389,7 @@
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>525</v>
+        <v>502</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -9613,7 +9402,7 @@
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>526</v>
+        <v>503</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -9626,7 +9415,7 @@
     </row>
     <row r="37" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="29" t="s">
-        <v>527</v>
+        <v>504</v>
       </c>
       <c r="B37" s="30" t="n">
         <f aca="false">IFERROR(COUNTIF(B22:B36,"Sim")/(COUNTA(B22:B36)-COUNTIF(B22:B36,"N/A")),0)</f>
@@ -9634,12 +9423,12 @@
       </c>
       <c r="C37" s="32"/>
       <c r="D37" s="12" t="s">
-        <v>528</v>
+        <v>505</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>529</v>
+        <v>506</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -9652,16 +9441,16 @@
     </row>
     <row r="40" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
@@ -9671,14 +9460,14 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>530</v>
+        <v>507</v>
       </c>
       <c r="B41" s="14"/>
       <c r="C41" s="12" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="D41" s="35" t="s">
-        <v>532</v>
+        <v>509</v>
       </c>
       <c r="E41" s="35"/>
       <c r="F41" s="35"/>
@@ -9688,11 +9477,11 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>533</v>
+        <v>510</v>
       </c>
       <c r="B42" s="14"/>
       <c r="C42" s="12" t="s">
-        <v>534</v>
+        <v>511</v>
       </c>
       <c r="D42" s="35"/>
       <c r="E42" s="35"/>
@@ -9703,11 +9492,11 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>535</v>
+        <v>512</v>
       </c>
       <c r="B43" s="14"/>
       <c r="C43" s="12" t="s">
-        <v>536</v>
+        <v>513</v>
       </c>
       <c r="D43" s="35"/>
       <c r="E43" s="35"/>
@@ -9718,14 +9507,14 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>537</v>
+        <v>514</v>
       </c>
       <c r="B44" s="26"/>
       <c r="C44" s="12" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="D44" s="35" t="s">
-        <v>539</v>
+        <v>516</v>
       </c>
       <c r="E44" s="35"/>
       <c r="F44" s="35"/>
@@ -9735,14 +9524,14 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>540</v>
+        <v>517</v>
       </c>
       <c r="B45" s="26"/>
       <c r="C45" s="12" t="s">
-        <v>541</v>
+        <v>518</v>
       </c>
       <c r="D45" s="35" t="s">
-        <v>542</v>
+        <v>519</v>
       </c>
       <c r="E45" s="35"/>
       <c r="F45" s="35"/>
@@ -9752,11 +9541,11 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>543</v>
+        <v>520</v>
       </c>
       <c r="B46" s="14"/>
       <c r="C46" s="12" t="s">
-        <v>544</v>
+        <v>521</v>
       </c>
       <c r="D46" s="35"/>
       <c r="E46" s="35"/>
@@ -9767,17 +9556,17 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="29" t="s">
-        <v>545</v>
+        <v>522</v>
       </c>
       <c r="B47" s="25" t="n">
         <f aca="false">IFERROR(B42*B43,0)</f>
         <v>0</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>534</v>
+        <v>511</v>
       </c>
       <c r="D47" s="35" t="s">
-        <v>546</v>
+        <v>523</v>
       </c>
       <c r="E47" s="35"/>
       <c r="F47" s="35"/>
@@ -9787,17 +9576,17 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="29" t="s">
-        <v>547</v>
+        <v>524</v>
       </c>
       <c r="B48" s="25" t="n">
         <f aca="false">IFERROR(B47*B41,0)</f>
         <v>0</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="D48" s="35" t="s">
-        <v>548</v>
+        <v>525</v>
       </c>
       <c r="E48" s="35"/>
       <c r="F48" s="35"/>
@@ -9878,7 +9667,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>549</v>
+        <v>526</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9894,7 +9683,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>550</v>
+        <v>527</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -9910,7 +9699,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>551</v>
+        <v>528</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -9926,16 +9715,16 @@
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
@@ -9948,14 +9737,14 @@
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>552</v>
+        <v>529</v>
       </c>
       <c r="B6" s="26"/>
       <c r="C6" s="12" t="s">
-        <v>553</v>
+        <v>530</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>554</v>
+        <v>531</v>
       </c>
       <c r="E6" s="35"/>
       <c r="F6" s="35"/>
@@ -9968,16 +9757,16 @@
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>555</v>
+        <v>532</v>
       </c>
       <c r="B7" s="16" t="n">
         <v>0.01</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>556</v>
+        <v>533</v>
       </c>
       <c r="E7" s="35"/>
       <c r="F7" s="35"/>
@@ -9990,17 +9779,17 @@
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>557</v>
+        <v>534</v>
       </c>
       <c r="B8" s="33" t="n">
         <f aca="false">IFERROR(B6*(1+B7),0)</f>
         <v>0</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>553</v>
+        <v>530</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>558</v>
+        <v>535</v>
       </c>
       <c r="E8" s="35"/>
       <c r="F8" s="35"/>
@@ -10013,16 +9802,16 @@
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>559</v>
+        <v>536</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.02</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>560</v>
+        <v>537</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="35"/>
@@ -10035,14 +9824,14 @@
     </row>
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>561</v>
+        <v>538</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="12" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>562</v>
+        <v>539</v>
       </c>
       <c r="E10" s="35"/>
       <c r="F10" s="35"/>
@@ -10055,14 +9844,14 @@
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>563</v>
+        <v>540</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="12" t="s">
-        <v>564</v>
+        <v>541</v>
       </c>
       <c r="D11" s="35" t="s">
-        <v>565</v>
+        <v>542</v>
       </c>
       <c r="E11" s="35"/>
       <c r="F11" s="35"/>
@@ -10075,17 +9864,17 @@
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>566</v>
+        <v>543</v>
       </c>
       <c r="B12" s="33" t="n">
         <f aca="false">IFERROR(B10/B11,0)</f>
         <v>0</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>567</v>
+        <v>544</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>568</v>
+        <v>545</v>
       </c>
       <c r="E12" s="35"/>
       <c r="F12" s="35"/>
@@ -10098,14 +9887,14 @@
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="B13" s="26"/>
       <c r="C13" s="12" t="s">
-        <v>567</v>
+        <v>544</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>570</v>
+        <v>547</v>
       </c>
       <c r="E13" s="35"/>
       <c r="F13" s="35"/>
@@ -10118,17 +9907,17 @@
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>571</v>
+        <v>548</v>
       </c>
       <c r="B14" s="33" t="n">
         <f aca="false">B12+B13</f>
         <v>0</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>567</v>
+        <v>544</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>572</v>
+        <v>549</v>
       </c>
       <c r="E14" s="35"/>
       <c r="F14" s="35"/>
@@ -10141,7 +9930,7 @@
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>573</v>
+        <v>550</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -10157,7 +9946,7 @@
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="39" t="s">
-        <v>574</v>
+        <v>551</v>
       </c>
       <c r="B17" s="39"/>
       <c r="C17" s="39"/>
@@ -10173,54 +9962,54 @@
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>575</v>
+        <v>552</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>576</v>
+        <v>553</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>577</v>
+        <v>554</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>578</v>
+        <v>555</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>579</v>
+        <v>556</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>580</v>
+        <v>557</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>581</v>
+        <v>558</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>583</v>
+        <v>560</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>584</v>
+        <v>561</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>585</v>
+        <v>562</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>586</v>
+        <v>563</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>587</v>
+        <v>564</v>
       </c>
       <c r="C19" s="16" t="n">
         <v>0.7</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="E19" s="27" t="n">
         <v>0.02</v>
@@ -10247,7 +10036,7 @@
       <c r="B20" s="11"/>
       <c r="C20" s="16"/>
       <c r="D20" s="11" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="E20" s="27"/>
       <c r="F20" s="27"/>
@@ -10272,7 +10061,7 @@
       <c r="B21" s="11"/>
       <c r="C21" s="16"/>
       <c r="D21" s="11" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="E21" s="27"/>
       <c r="F21" s="27"/>
@@ -10297,7 +10086,7 @@
       <c r="B22" s="11"/>
       <c r="C22" s="16"/>
       <c r="D22" s="11" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="E22" s="27"/>
       <c r="F22" s="27"/>
@@ -10322,7 +10111,7 @@
       <c r="B23" s="11"/>
       <c r="C23" s="16"/>
       <c r="D23" s="11" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="E23" s="27"/>
       <c r="F23" s="27"/>
@@ -10347,7 +10136,7 @@
       <c r="B24" s="11"/>
       <c r="C24" s="16"/>
       <c r="D24" s="11" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="E24" s="27"/>
       <c r="F24" s="27"/>
@@ -10372,7 +10161,7 @@
       <c r="B25" s="11"/>
       <c r="C25" s="16"/>
       <c r="D25" s="11" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="E25" s="27"/>
       <c r="F25" s="27"/>
@@ -10397,7 +10186,7 @@
       <c r="B26" s="11"/>
       <c r="C26" s="16"/>
       <c r="D26" s="11" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="E26" s="27"/>
       <c r="F26" s="27"/>
@@ -10422,7 +10211,7 @@
       <c r="B27" s="11"/>
       <c r="C27" s="16"/>
       <c r="D27" s="11" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="E27" s="27"/>
       <c r="F27" s="27"/>
@@ -10447,7 +10236,7 @@
       <c r="B28" s="11"/>
       <c r="C28" s="16"/>
       <c r="D28" s="11" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="E28" s="27"/>
       <c r="F28" s="27"/>
@@ -10472,7 +10261,7 @@
       <c r="B29" s="11"/>
       <c r="C29" s="16"/>
       <c r="D29" s="11" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="E29" s="27"/>
       <c r="F29" s="27"/>
@@ -10497,7 +10286,7 @@
       <c r="B30" s="11"/>
       <c r="C30" s="16"/>
       <c r="D30" s="11" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="E30" s="27"/>
       <c r="F30" s="27"/>
@@ -10522,7 +10311,7 @@
       <c r="B31" s="11"/>
       <c r="C31" s="16"/>
       <c r="D31" s="11" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="E31" s="27"/>
       <c r="F31" s="27"/>
@@ -10547,7 +10336,7 @@
       <c r="B32" s="11"/>
       <c r="C32" s="16"/>
       <c r="D32" s="11" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="E32" s="27"/>
       <c r="F32" s="27"/>
@@ -10569,7 +10358,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="29" t="s">
-        <v>588</v>
+        <v>565</v>
       </c>
       <c r="B33" s="32"/>
       <c r="C33" s="30" t="n">
@@ -10594,7 +10383,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="29" t="s">
-        <v>589</v>
+        <v>566</v>
       </c>
       <c r="B34" s="32"/>
       <c r="C34" s="5" t="str">
@@ -10613,7 +10402,7 @@
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="39" t="s">
-        <v>590</v>
+        <v>567</v>
       </c>
       <c r="B35" s="39"/>
       <c r="C35" s="39"/>
@@ -10629,7 +10418,7 @@
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>591</v>
+        <v>568</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -10645,7 +10434,7 @@
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="39" t="s">
-        <v>592</v>
+        <v>569</v>
       </c>
       <c r="B38" s="39"/>
       <c r="C38" s="39"/>
@@ -10661,50 +10450,50 @@
     </row>
     <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>478</v>
+        <v>455</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>593</v>
+        <v>570</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>594</v>
+        <v>571</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>595</v>
+        <v>572</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>580</v>
+        <v>557</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>596</v>
+        <v>573</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>597</v>
+        <v>574</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>583</v>
+        <v>560</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>584</v>
+        <v>561</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>598</v>
+        <v>575</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="26"/>
       <c r="D40" s="11" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="E40" s="27"/>
       <c r="F40" s="27"/>
@@ -10723,17 +10512,17 @@
         <v/>
       </c>
       <c r="L40" s="11" t="s">
-        <v>600</v>
+        <v>577</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>601</v>
+        <v>578</v>
       </c>
       <c r="B41" s="11"/>
       <c r="C41" s="26"/>
       <c r="D41" s="11" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="E41" s="27"/>
       <c r="F41" s="27"/>
@@ -10752,17 +10541,17 @@
         <v/>
       </c>
       <c r="L41" s="11" t="s">
-        <v>600</v>
+        <v>577</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>602</v>
+        <v>579</v>
       </c>
       <c r="B42" s="11"/>
       <c r="C42" s="26"/>
       <c r="D42" s="11" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="E42" s="27"/>
       <c r="F42" s="27"/>
@@ -10781,17 +10570,17 @@
         <v/>
       </c>
       <c r="L42" s="11" t="s">
-        <v>600</v>
+        <v>577</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>603</v>
+        <v>580</v>
       </c>
       <c r="B43" s="11"/>
       <c r="C43" s="26"/>
       <c r="D43" s="11" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="E43" s="27"/>
       <c r="F43" s="27"/>
@@ -10810,17 +10599,17 @@
         <v/>
       </c>
       <c r="L43" s="11" t="s">
-        <v>600</v>
+        <v>577</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>604</v>
+        <v>581</v>
       </c>
       <c r="B44" s="11"/>
       <c r="C44" s="26"/>
       <c r="D44" s="11" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="E44" s="27"/>
       <c r="F44" s="27"/>
@@ -10839,17 +10628,17 @@
         <v/>
       </c>
       <c r="L44" s="11" t="s">
-        <v>605</v>
+        <v>582</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>606</v>
+        <v>583</v>
       </c>
       <c r="B45" s="11"/>
       <c r="C45" s="26"/>
       <c r="D45" s="11" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="E45" s="27"/>
       <c r="F45" s="27"/>
@@ -10868,17 +10657,17 @@
         <v/>
       </c>
       <c r="L45" s="11" t="s">
-        <v>605</v>
+        <v>582</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>497</v>
+        <v>474</v>
       </c>
       <c r="B46" s="11"/>
       <c r="C46" s="26"/>
       <c r="D46" s="11" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="E46" s="27"/>
       <c r="F46" s="27"/>
@@ -10897,17 +10686,17 @@
         <v/>
       </c>
       <c r="L46" s="11" t="s">
-        <v>607</v>
+        <v>584</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>608</v>
+        <v>585</v>
       </c>
       <c r="B47" s="11"/>
       <c r="C47" s="26"/>
       <c r="D47" s="11" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="E47" s="27"/>
       <c r="F47" s="27"/>
@@ -10926,17 +10715,17 @@
         <v/>
       </c>
       <c r="L47" s="11" t="s">
-        <v>607</v>
+        <v>584</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="s">
-        <v>501</v>
+        <v>478</v>
       </c>
       <c r="B48" s="11"/>
       <c r="C48" s="26"/>
       <c r="D48" s="11" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="E48" s="27"/>
       <c r="F48" s="27"/>
@@ -10958,7 +10747,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="29" t="s">
-        <v>609</v>
+        <v>586</v>
       </c>
       <c r="B49" s="32"/>
       <c r="C49" s="32"/>
@@ -10980,7 +10769,7 @@
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>610</v>
+        <v>587</v>
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -10996,7 +10785,7 @@
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="39" t="s">
-        <v>611</v>
+        <v>588</v>
       </c>
       <c r="B52" s="39"/>
       <c r="C52" s="39"/>
@@ -11012,16 +10801,16 @@
     </row>
     <row r="53" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
@@ -11034,14 +10823,14 @@
     </row>
     <row r="54" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>612</v>
+        <v>589</v>
       </c>
       <c r="B54" s="26"/>
       <c r="C54" s="12" t="s">
-        <v>613</v>
+        <v>590</v>
       </c>
       <c r="D54" s="35" t="s">
-        <v>614</v>
+        <v>591</v>
       </c>
       <c r="E54" s="35"/>
       <c r="F54" s="35"/>
@@ -11054,14 +10843,14 @@
     </row>
     <row r="55" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
-        <v>615</v>
+        <v>592</v>
       </c>
       <c r="B55" s="27"/>
       <c r="C55" s="12" t="s">
-        <v>616</v>
+        <v>593</v>
       </c>
       <c r="D55" s="35" t="s">
-        <v>617</v>
+        <v>594</v>
       </c>
       <c r="E55" s="35"/>
       <c r="F55" s="35"/>
@@ -11074,16 +10863,16 @@
     </row>
     <row r="56" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
-        <v>618</v>
+        <v>595</v>
       </c>
       <c r="B56" s="16" t="n">
         <v>0.02</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D56" s="35" t="s">
-        <v>619</v>
+        <v>596</v>
       </c>
       <c r="E56" s="35"/>
       <c r="F56" s="35"/>
@@ -11096,14 +10885,14 @@
     </row>
     <row r="57" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
-        <v>620</v>
+        <v>597</v>
       </c>
       <c r="B57" s="27"/>
       <c r="C57" s="12" t="s">
-        <v>616</v>
+        <v>593</v>
       </c>
       <c r="D57" s="35" t="s">
-        <v>621</v>
+        <v>598</v>
       </c>
       <c r="E57" s="35"/>
       <c r="F57" s="35"/>
@@ -11116,17 +10905,17 @@
     </row>
     <row r="58" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
-        <v>622</v>
+        <v>599</v>
       </c>
       <c r="B58" s="31" t="n">
         <f aca="false">IFERROR(B54/1000*(B55*(1-B56)+B57*B56),0)</f>
         <v>0</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>623</v>
+        <v>600</v>
       </c>
       <c r="D58" s="35" t="s">
-        <v>624</v>
+        <v>601</v>
       </c>
       <c r="E58" s="35"/>
       <c r="F58" s="35"/>
@@ -11139,16 +10928,16 @@
     </row>
     <row r="59" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
-        <v>625</v>
+        <v>602</v>
       </c>
       <c r="B59" s="16" t="n">
         <v>0.03</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D59" s="35" t="s">
-        <v>626</v>
+        <v>603</v>
       </c>
       <c r="E59" s="35"/>
       <c r="F59" s="35"/>
@@ -11161,17 +10950,17 @@
     </row>
     <row r="60" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
-        <v>627</v>
+        <v>604</v>
       </c>
       <c r="B60" s="31" t="n">
         <f aca="false">IFERROR(B58/(1-B59),0)</f>
         <v>0</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>623</v>
+        <v>600</v>
       </c>
       <c r="D60" s="35" t="s">
-        <v>628</v>
+        <v>605</v>
       </c>
       <c r="E60" s="35"/>
       <c r="F60" s="35"/>
@@ -11184,16 +10973,16 @@
     </row>
     <row r="61" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="s">
-        <v>629</v>
+        <v>606</v>
       </c>
       <c r="B61" s="14" t="n">
         <v>1</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>630</v>
+        <v>607</v>
       </c>
       <c r="D61" s="35" t="s">
-        <v>631</v>
+        <v>608</v>
       </c>
       <c r="E61" s="35"/>
       <c r="F61" s="35"/>
@@ -11206,14 +10995,14 @@
     </row>
     <row r="62" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="10" t="s">
-        <v>632</v>
+        <v>609</v>
       </c>
       <c r="B62" s="26"/>
       <c r="C62" s="12" t="s">
-        <v>633</v>
+        <v>610</v>
       </c>
       <c r="D62" s="35" t="s">
-        <v>634</v>
+        <v>611</v>
       </c>
       <c r="E62" s="35"/>
       <c r="F62" s="35"/>
@@ -11226,17 +11015,17 @@
     </row>
     <row r="63" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="s">
-        <v>635</v>
+        <v>612</v>
       </c>
       <c r="B63" s="25" t="n">
         <f aca="false">IFERROR(3600/B62*B61,0)</f>
         <v>0</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>636</v>
+        <v>613</v>
       </c>
       <c r="D63" s="35" t="s">
-        <v>637</v>
+        <v>614</v>
       </c>
       <c r="E63" s="35"/>
       <c r="F63" s="35"/>
@@ -11249,14 +11038,14 @@
     </row>
     <row r="64" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="s">
-        <v>638</v>
+        <v>615</v>
       </c>
       <c r="B64" s="27"/>
       <c r="C64" s="12" t="s">
-        <v>639</v>
+        <v>616</v>
       </c>
       <c r="D64" s="35" t="s">
-        <v>640</v>
+        <v>617</v>
       </c>
       <c r="E64" s="35"/>
       <c r="F64" s="35"/>
@@ -11269,17 +11058,17 @@
     </row>
     <row r="65" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="10" t="s">
-        <v>641</v>
+        <v>618</v>
       </c>
       <c r="B65" s="31" t="n">
         <f aca="false">IFERROR(B64/B63,0)</f>
         <v>0</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>623</v>
+        <v>600</v>
       </c>
       <c r="D65" s="35" t="s">
-        <v>642</v>
+        <v>619</v>
       </c>
       <c r="E65" s="35"/>
       <c r="F65" s="35"/>
@@ -11292,14 +11081,14 @@
     </row>
     <row r="66" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="s">
-        <v>643</v>
+        <v>620</v>
       </c>
       <c r="B66" s="27"/>
       <c r="C66" s="12" t="s">
-        <v>623</v>
+        <v>600</v>
       </c>
       <c r="D66" s="35" t="s">
-        <v>644</v>
+        <v>621</v>
       </c>
       <c r="E66" s="35"/>
       <c r="F66" s="35"/>
@@ -11312,17 +11101,17 @@
     </row>
     <row r="67" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="38" t="s">
-        <v>645</v>
+        <v>622</v>
       </c>
       <c r="B67" s="31" t="n">
         <f aca="false">B60+B65+B66</f>
         <v>0</v>
       </c>
       <c r="C67" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="D67" s="35" t="s">
         <v>623</v>
-      </c>
-      <c r="D67" s="35" t="s">
-        <v>646</v>
       </c>
       <c r="E67" s="35"/>
       <c r="F67" s="35"/>
@@ -11335,7 +11124,7 @@
     </row>
     <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
-        <v>647</v>
+        <v>624</v>
       </c>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -11351,7 +11140,7 @@
     </row>
     <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="39" t="s">
-        <v>648</v>
+        <v>625</v>
       </c>
       <c r="B70" s="39"/>
       <c r="C70" s="39"/>
@@ -11367,45 +11156,45 @@
     </row>
     <row r="71" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
-        <v>649</v>
+        <v>626</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>650</v>
+        <v>627</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>651</v>
+        <v>628</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>652</v>
+        <v>629</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>653</v>
+        <v>630</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>654</v>
+        <v>631</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>655</v>
+        <v>632</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>656</v>
+        <v>633</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>657</v>
+        <v>634</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>583</v>
+        <v>560</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>584</v>
+        <v>561</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>658</v>
+        <v>635</v>
       </c>
       <c r="B72" s="14"/>
       <c r="C72" s="15"/>
@@ -11443,7 +11232,7 @@
     </row>
     <row r="73" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="10" t="s">
-        <v>659</v>
+        <v>636</v>
       </c>
       <c r="B73" s="14"/>
       <c r="C73" s="15"/>
@@ -11481,7 +11270,7 @@
     </row>
     <row r="74" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="s">
-        <v>660</v>
+        <v>637</v>
       </c>
       <c r="B74" s="14"/>
       <c r="C74" s="15"/>
@@ -11519,7 +11308,7 @@
     </row>
     <row r="75" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="10" t="s">
-        <v>661</v>
+        <v>638</v>
       </c>
       <c r="B75" s="14"/>
       <c r="C75" s="15"/>
@@ -11557,7 +11346,7 @@
     </row>
     <row r="76" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="10" t="s">
-        <v>662</v>
+        <v>639</v>
       </c>
       <c r="B76" s="14"/>
       <c r="C76" s="15"/>
@@ -11595,7 +11384,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="29" t="s">
-        <v>663</v>
+        <v>640</v>
       </c>
       <c r="B77" s="32"/>
       <c r="C77" s="32"/>
@@ -11623,7 +11412,7 @@
     </row>
     <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="39" t="s">
-        <v>664</v>
+        <v>641</v>
       </c>
       <c r="B78" s="39"/>
       <c r="C78" s="39"/>
@@ -11639,7 +11428,7 @@
     </row>
     <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
-        <v>665</v>
+        <v>642</v>
       </c>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -11655,7 +11444,7 @@
     </row>
     <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="39" t="s">
-        <v>666</v>
+        <v>643</v>
       </c>
       <c r="B81" s="39"/>
       <c r="C81" s="39"/>
@@ -11671,16 +11460,16 @@
     </row>
     <row r="82" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="s">
-        <v>667</v>
+        <v>644</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>668</v>
+        <v>645</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>669</v>
+        <v>646</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="E82" s="4"/>
       <c r="F82" s="4"/>
@@ -11693,14 +11482,14 @@
     </row>
     <row r="83" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="s">
-        <v>670</v>
+        <v>647</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>671</v>
+        <v>648</v>
       </c>
       <c r="C83" s="15"/>
       <c r="D83" s="35" t="s">
-        <v>672</v>
+        <v>649</v>
       </c>
       <c r="E83" s="35"/>
       <c r="F83" s="35"/>
@@ -11713,14 +11502,14 @@
     </row>
     <row r="84" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="10" t="s">
-        <v>673</v>
+        <v>650</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>674</v>
+        <v>651</v>
       </c>
       <c r="C84" s="15"/>
       <c r="D84" s="35" t="s">
-        <v>675</v>
+        <v>652</v>
       </c>
       <c r="E84" s="35"/>
       <c r="F84" s="35"/>
@@ -11733,14 +11522,14 @@
     </row>
     <row r="85" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="10" t="s">
-        <v>676</v>
+        <v>653</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>677</v>
+        <v>654</v>
       </c>
       <c r="C85" s="15"/>
       <c r="D85" s="35" t="s">
-        <v>678</v>
+        <v>655</v>
       </c>
       <c r="E85" s="35"/>
       <c r="F85" s="35"/>
@@ -11753,14 +11542,14 @@
     </row>
     <row r="86" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="10" t="s">
-        <v>679</v>
+        <v>656</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>677</v>
+        <v>654</v>
       </c>
       <c r="C86" s="15"/>
       <c r="D86" s="35" t="s">
-        <v>680</v>
+        <v>657</v>
       </c>
       <c r="E86" s="35"/>
       <c r="F86" s="35"/>
@@ -11773,14 +11562,14 @@
     </row>
     <row r="87" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="10" t="s">
-        <v>681</v>
+        <v>658</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>674</v>
+        <v>651</v>
       </c>
       <c r="C87" s="15"/>
       <c r="D87" s="35" t="s">
-        <v>682</v>
+        <v>659</v>
       </c>
       <c r="E87" s="35"/>
       <c r="F87" s="35"/>
@@ -11793,14 +11582,14 @@
     </row>
     <row r="88" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="10" t="s">
-        <v>683</v>
+        <v>660</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>671</v>
+        <v>648</v>
       </c>
       <c r="C88" s="15"/>
       <c r="D88" s="35" t="s">
-        <v>684</v>
+        <v>661</v>
       </c>
       <c r="E88" s="35"/>
       <c r="F88" s="35"/>
@@ -11813,14 +11602,14 @@
     </row>
     <row r="89" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="10" t="s">
-        <v>685</v>
+        <v>662</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>671</v>
+        <v>648</v>
       </c>
       <c r="C89" s="15"/>
       <c r="D89" s="35" t="s">
-        <v>686</v>
+        <v>663</v>
       </c>
       <c r="E89" s="35"/>
       <c r="F89" s="35"/>
@@ -11833,14 +11622,14 @@
     </row>
     <row r="90" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="10" t="s">
-        <v>687</v>
+        <v>664</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>671</v>
+        <v>648</v>
       </c>
       <c r="C90" s="15"/>
       <c r="D90" s="35" t="s">
-        <v>688</v>
+        <v>665</v>
       </c>
       <c r="E90" s="35"/>
       <c r="F90" s="35"/>
@@ -11853,14 +11642,14 @@
     </row>
     <row r="91" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="10" t="s">
-        <v>689</v>
+        <v>666</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>674</v>
+        <v>651</v>
       </c>
       <c r="C91" s="15"/>
       <c r="D91" s="35" t="s">
-        <v>690</v>
+        <v>667</v>
       </c>
       <c r="E91" s="35"/>
       <c r="F91" s="35"/>
@@ -11873,10 +11662,10 @@
     </row>
     <row r="92" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="10" t="s">
-        <v>691</v>
+        <v>668</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>671</v>
+        <v>648</v>
       </c>
       <c r="C92" s="15"/>
       <c r="D92" s="35"/>
@@ -11891,14 +11680,14 @@
     </row>
     <row r="93" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="10" t="s">
-        <v>692</v>
+        <v>669</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>671</v>
+        <v>648</v>
       </c>
       <c r="C93" s="15"/>
       <c r="D93" s="35" t="s">
-        <v>693</v>
+        <v>670</v>
       </c>
       <c r="E93" s="35"/>
       <c r="F93" s="35"/>
@@ -11911,7 +11700,7 @@
     </row>
     <row r="94" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="10" t="s">
-        <v>694</v>
+        <v>671</v>
       </c>
       <c r="B94" s="11"/>
       <c r="C94" s="15"/>
@@ -11927,7 +11716,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="29" t="s">
-        <v>695</v>
+        <v>672</v>
       </c>
       <c r="B95" s="32"/>
       <c r="C95" s="28" t="n">
@@ -11946,16 +11735,16 @@
     </row>
     <row r="96" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="s">
-        <v>696</v>
+        <v>673</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
@@ -11968,14 +11757,14 @@
     </row>
     <row r="97" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="10" t="s">
-        <v>697</v>
+        <v>674</v>
       </c>
       <c r="B97" s="14"/>
       <c r="C97" s="12" t="s">
-        <v>567</v>
+        <v>544</v>
       </c>
       <c r="D97" s="35" t="s">
-        <v>698</v>
+        <v>675</v>
       </c>
       <c r="E97" s="35"/>
       <c r="F97" s="35"/>
@@ -11988,17 +11777,17 @@
     </row>
     <row r="98" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="10" t="s">
-        <v>699</v>
+        <v>676</v>
       </c>
       <c r="B98" s="31" t="n">
         <f aca="false">IFERROR(C95/B97,0)</f>
         <v>0</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>639</v>
+        <v>616</v>
       </c>
       <c r="D98" s="35" t="s">
-        <v>700</v>
+        <v>677</v>
       </c>
       <c r="E98" s="35"/>
       <c r="F98" s="35"/>
@@ -12011,17 +11800,17 @@
     </row>
     <row r="99" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="10" t="s">
-        <v>701</v>
+        <v>678</v>
       </c>
       <c r="B99" s="31" t="n">
         <f aca="false">IFERROR(B98*$B$14/$B$10,0)</f>
         <v>0</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D99" s="35" t="s">
-        <v>702</v>
+        <v>679</v>
       </c>
       <c r="E99" s="35"/>
       <c r="F99" s="35"/>
@@ -12034,14 +11823,14 @@
     </row>
     <row r="100" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="10" t="s">
-        <v>703</v>
+        <v>680</v>
       </c>
       <c r="B100" s="27"/>
       <c r="C100" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D100" s="35" t="s">
-        <v>704</v>
+        <v>681</v>
       </c>
       <c r="E100" s="35"/>
       <c r="F100" s="35"/>
@@ -12054,17 +11843,17 @@
     </row>
     <row r="101" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="38" t="s">
-        <v>705</v>
+        <v>682</v>
       </c>
       <c r="B101" s="31" t="n">
         <f aca="false">B99+B100</f>
         <v>0</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D101" s="35" t="s">
-        <v>706</v>
+        <v>683</v>
       </c>
       <c r="E101" s="35"/>
       <c r="F101" s="35"/>
@@ -12077,7 +11866,7 @@
     </row>
     <row r="103" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="s">
-        <v>707</v>
+        <v>684</v>
       </c>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -12093,7 +11882,7 @@
     </row>
     <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="39" t="s">
-        <v>708</v>
+        <v>685</v>
       </c>
       <c r="B104" s="39"/>
       <c r="C104" s="39"/>
@@ -12112,44 +11901,44 @@
         <v>42</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>709</v>
+        <v>686</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>710</v>
+        <v>687</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>711</v>
+        <v>688</v>
       </c>
       <c r="F105" s="4"/>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
       <c r="I105" s="4"/>
       <c r="J105" s="4" t="s">
-        <v>583</v>
+        <v>560</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>584</v>
+        <v>561</v>
       </c>
       <c r="L105" s="4" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="10" t="s">
-        <v>712</v>
+        <v>689</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>713</v>
+        <v>690</v>
       </c>
       <c r="C106" s="15"/>
       <c r="D106" s="12" t="s">
-        <v>714</v>
+        <v>691</v>
       </c>
       <c r="E106" s="12" t="s">
-        <v>715</v>
+        <v>692</v>
       </c>
       <c r="J106" s="31" t="n">
         <f aca="false">IFERROR(C106/$B$10,0)</f>
@@ -12163,17 +11952,17 @@
     </row>
     <row r="107" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="10" t="s">
-        <v>716</v>
+        <v>693</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>717</v>
+        <v>694</v>
       </c>
       <c r="C107" s="14"/>
       <c r="D107" s="12" t="s">
-        <v>718</v>
+        <v>695</v>
       </c>
       <c r="E107" s="12" t="s">
-        <v>719</v>
+        <v>696</v>
       </c>
       <c r="J107" s="31" t="n">
         <f aca="false">IFERROR(C107/$B$10*(J33+J49),0)</f>
@@ -12190,11 +11979,11 @@
         <v>58</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>720</v>
+        <v>697</v>
       </c>
       <c r="C108" s="15"/>
       <c r="D108" s="12" t="s">
-        <v>721</v>
+        <v>698</v>
       </c>
       <c r="E108" s="14"/>
       <c r="J108" s="31" t="n">
@@ -12206,7 +11995,7 @@
         <v/>
       </c>
       <c r="L108" s="11" t="s">
-        <v>722</v>
+        <v>699</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12214,14 +12003,14 @@
         <v>64</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>723</v>
+        <v>700</v>
       </c>
       <c r="C109" s="16"/>
       <c r="D109" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="E109" s="12" t="s">
-        <v>724</v>
+        <v>701</v>
       </c>
       <c r="J109" s="31" t="n">
         <f aca="false">IFERROR(C109*$B$129,0)</f>
@@ -12235,17 +12024,17 @@
     </row>
     <row r="110" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="10" t="s">
-        <v>725</v>
+        <v>702</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>726</v>
+        <v>703</v>
       </c>
       <c r="C110" s="27"/>
       <c r="D110" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="E110" s="12" t="s">
-        <v>727</v>
+        <v>704</v>
       </c>
       <c r="J110" s="31" t="n">
         <f aca="false">C110</f>
@@ -12259,17 +12048,17 @@
     </row>
     <row r="111" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="10" t="s">
-        <v>728</v>
+        <v>705</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>729</v>
+        <v>706</v>
       </c>
       <c r="C111" s="16"/>
       <c r="D111" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="E111" s="12" t="s">
-        <v>730</v>
+        <v>707</v>
       </c>
       <c r="J111" s="31" t="n">
         <f aca="false">IFERROR(C111*(J33+J49),0)</f>
@@ -12286,11 +12075,11 @@
         <v>62</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>731</v>
+        <v>708</v>
       </c>
       <c r="C112" s="16"/>
       <c r="D112" s="12" t="s">
-        <v>732</v>
+        <v>709</v>
       </c>
       <c r="E112" s="14"/>
       <c r="J112" s="31" t="n">
@@ -12302,19 +12091,19 @@
         <v/>
       </c>
       <c r="L112" s="11" t="s">
-        <v>733</v>
+        <v>710</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="10" t="s">
-        <v>734</v>
+        <v>711</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>726</v>
+        <v>703</v>
       </c>
       <c r="C113" s="27"/>
       <c r="D113" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="E113" s="11"/>
       <c r="J113" s="31" t="n">
@@ -12329,7 +12118,7 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="29" t="s">
-        <v>735</v>
+        <v>712</v>
       </c>
       <c r="B114" s="32"/>
       <c r="C114" s="32"/>
@@ -12351,7 +12140,7 @@
     </row>
     <row r="116" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
-        <v>736</v>
+        <v>713</v>
       </c>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -12367,19 +12156,19 @@
     </row>
     <row r="117" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="4" t="s">
-        <v>737</v>
+        <v>714</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>583</v>
+        <v>560</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>738</v>
+        <v>715</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>739</v>
+        <v>716</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>740</v>
+        <v>717</v>
       </c>
       <c r="F117" s="4"/>
       <c r="G117" s="4"/>
@@ -12391,7 +12180,7 @@
     </row>
     <row r="118" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="10" t="s">
-        <v>741</v>
+        <v>718</v>
       </c>
       <c r="B118" s="18" t="n">
         <f aca="false">J33</f>
@@ -12406,7 +12195,7 @@
         <v>0</v>
       </c>
       <c r="E118" s="35" t="s">
-        <v>742</v>
+        <v>719</v>
       </c>
       <c r="F118" s="35"/>
       <c r="G118" s="35"/>
@@ -12418,7 +12207,7 @@
     </row>
     <row r="119" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="10" t="s">
-        <v>743</v>
+        <v>720</v>
       </c>
       <c r="B119" s="18" t="n">
         <f aca="false">J49</f>
@@ -12433,7 +12222,7 @@
         <v>0</v>
       </c>
       <c r="E119" s="35" t="s">
-        <v>744</v>
+        <v>721</v>
       </c>
       <c r="F119" s="35"/>
       <c r="G119" s="35"/>
@@ -12445,7 +12234,7 @@
     </row>
     <row r="120" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="10" t="s">
-        <v>745</v>
+        <v>722</v>
       </c>
       <c r="B120" s="18" t="n">
         <f aca="false">J77</f>
@@ -12460,7 +12249,7 @@
         <v>0</v>
       </c>
       <c r="E120" s="35" t="s">
-        <v>746</v>
+        <v>723</v>
       </c>
       <c r="F120" s="35"/>
       <c r="G120" s="35"/>
@@ -12472,7 +12261,7 @@
     </row>
     <row r="121" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="10" t="s">
-        <v>747</v>
+        <v>724</v>
       </c>
       <c r="B121" s="18" t="n">
         <f aca="false">B101</f>
@@ -12487,7 +12276,7 @@
         <v>0</v>
       </c>
       <c r="E121" s="35" t="s">
-        <v>748</v>
+        <v>725</v>
       </c>
       <c r="F121" s="35"/>
       <c r="G121" s="35"/>
@@ -12499,7 +12288,7 @@
     </row>
     <row r="122" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="10" t="s">
-        <v>749</v>
+        <v>726</v>
       </c>
       <c r="B122" s="18" t="n">
         <f aca="false">J114</f>
@@ -12514,7 +12303,7 @@
         <v>0</v>
       </c>
       <c r="E122" s="35" t="s">
-        <v>750</v>
+        <v>727</v>
       </c>
       <c r="F122" s="35"/>
       <c r="G122" s="35"/>
@@ -12526,7 +12315,7 @@
     </row>
     <row r="123" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="41" t="s">
-        <v>751</v>
+        <v>728</v>
       </c>
       <c r="B123" s="31" t="n">
         <f aca="false">SUM(B118:B122)</f>
@@ -12541,7 +12330,7 @@
         <v>0</v>
       </c>
       <c r="E123" s="35" t="s">
-        <v>752</v>
+        <v>729</v>
       </c>
       <c r="F123" s="35"/>
       <c r="G123" s="35"/>
@@ -12553,7 +12342,7 @@
     </row>
     <row r="125" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="3" t="s">
-        <v>753</v>
+        <v>730</v>
       </c>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -12569,7 +12358,7 @@
     </row>
     <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="42" t="s">
-        <v>754</v>
+        <v>731</v>
       </c>
       <c r="B126" s="42"/>
       <c r="C126" s="42"/>
@@ -12602,13 +12391,13 @@
         <v>42</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="E128" s="4"/>
       <c r="F128" s="4"/>
@@ -12621,14 +12410,14 @@
     </row>
     <row r="129" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="10" t="s">
-        <v>755</v>
+        <v>732</v>
       </c>
       <c r="B129" s="27"/>
       <c r="C129" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D129" s="35" t="s">
-        <v>756</v>
+        <v>733</v>
       </c>
       <c r="E129" s="35"/>
       <c r="F129" s="35"/>
@@ -12641,14 +12430,14 @@
     </row>
     <row r="130" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="10" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="B130" s="16"/>
       <c r="C130" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D130" s="35" t="s">
-        <v>758</v>
+        <v>735</v>
       </c>
       <c r="E130" s="35"/>
       <c r="F130" s="35"/>
@@ -12661,14 +12450,14 @@
     </row>
     <row r="131" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="10" t="s">
-        <v>759</v>
+        <v>736</v>
       </c>
       <c r="B131" s="16"/>
       <c r="C131" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D131" s="35" t="s">
-        <v>760</v>
+        <v>737</v>
       </c>
       <c r="E131" s="35"/>
       <c r="F131" s="35"/>
@@ -12681,16 +12470,16 @@
     </row>
     <row r="132" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="10" t="s">
-        <v>761</v>
+        <v>738</v>
       </c>
       <c r="B132" s="16" t="n">
         <v>0.0165</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D132" s="35" t="s">
-        <v>762</v>
+        <v>739</v>
       </c>
       <c r="E132" s="35"/>
       <c r="F132" s="35"/>
@@ -12703,16 +12492,16 @@
     </row>
     <row r="133" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="10" t="s">
-        <v>763</v>
+        <v>740</v>
       </c>
       <c r="B133" s="16" t="n">
         <v>0.076</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D133" s="35" t="s">
-        <v>762</v>
+        <v>739</v>
       </c>
       <c r="E133" s="35"/>
       <c r="F133" s="35"/>
@@ -12725,14 +12514,14 @@
     </row>
     <row r="134" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="10" t="s">
-        <v>764</v>
+        <v>741</v>
       </c>
       <c r="B134" s="16"/>
       <c r="C134" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D134" s="35" t="s">
-        <v>765</v>
+        <v>742</v>
       </c>
       <c r="E134" s="35"/>
       <c r="F134" s="35"/>
@@ -12745,14 +12534,14 @@
     </row>
     <row r="135" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="10" t="s">
-        <v>766</v>
+        <v>743</v>
       </c>
       <c r="B135" s="16"/>
       <c r="C135" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D135" s="35" t="s">
-        <v>767</v>
+        <v>744</v>
       </c>
       <c r="E135" s="35"/>
       <c r="F135" s="35"/>
@@ -12765,14 +12554,14 @@
     </row>
     <row r="136" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="10" t="s">
-        <v>768</v>
+        <v>745</v>
       </c>
       <c r="B136" s="16"/>
       <c r="C136" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D136" s="35" t="s">
-        <v>769</v>
+        <v>746</v>
       </c>
       <c r="E136" s="35"/>
       <c r="F136" s="35"/>
@@ -12785,17 +12574,17 @@
     </row>
     <row r="137" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="10" t="s">
-        <v>770</v>
+        <v>747</v>
       </c>
       <c r="B137" s="31" t="n">
         <f aca="false">B129*B130</f>
         <v>0</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D137" s="35" t="s">
-        <v>771</v>
+        <v>748</v>
       </c>
       <c r="E137" s="35"/>
       <c r="F137" s="35"/>
@@ -12808,17 +12597,17 @@
     </row>
     <row r="138" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="10" t="s">
-        <v>772</v>
+        <v>749</v>
       </c>
       <c r="B138" s="31" t="n">
         <f aca="false">(B129+B137)*(1+B134)</f>
         <v>0</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D138" s="35" t="s">
-        <v>773</v>
+        <v>750</v>
       </c>
       <c r="E138" s="35"/>
       <c r="F138" s="35"/>
@@ -12831,17 +12620,17 @@
     </row>
     <row r="139" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="10" t="s">
-        <v>774</v>
+        <v>751</v>
       </c>
       <c r="B139" s="31" t="n">
         <f aca="false">MAX(0,B138*B135-B129*B131)</f>
         <v>0</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D139" s="35" t="s">
-        <v>775</v>
+        <v>752</v>
       </c>
       <c r="E139" s="35"/>
       <c r="F139" s="35"/>
@@ -12854,17 +12643,17 @@
     </row>
     <row r="140" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="38" t="s">
-        <v>776</v>
+        <v>753</v>
       </c>
       <c r="B140" s="31" t="n">
         <f aca="false">B129+B137+B139</f>
         <v>0</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D140" s="35" t="s">
-        <v>777</v>
+        <v>754</v>
       </c>
       <c r="E140" s="35"/>
       <c r="F140" s="35"/>
@@ -12877,16 +12666,16 @@
     </row>
     <row r="142" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="4" t="s">
-        <v>778</v>
+        <v>755</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="E142" s="4"/>
       <c r="F142" s="4"/>
@@ -12899,17 +12688,17 @@
     </row>
     <row r="143" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="10" t="s">
-        <v>779</v>
+        <v>756</v>
       </c>
       <c r="B143" s="31" t="n">
         <f aca="false">B129</f>
         <v>0</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D143" s="35" t="s">
-        <v>780</v>
+        <v>757</v>
       </c>
       <c r="E143" s="35"/>
       <c r="F143" s="35"/>
@@ -12922,17 +12711,17 @@
     </row>
     <row r="144" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="10" t="s">
-        <v>781</v>
+        <v>758</v>
       </c>
       <c r="B144" s="31" t="n">
         <f aca="false">-B129*B131</f>
         <v>-0</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D144" s="35" t="s">
-        <v>782</v>
+        <v>759</v>
       </c>
       <c r="E144" s="35"/>
       <c r="F144" s="35"/>
@@ -12945,17 +12734,17 @@
     </row>
     <row r="145" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="10" t="s">
-        <v>783</v>
+        <v>760</v>
       </c>
       <c r="B145" s="31" t="n">
         <f aca="false">-B129*B132</f>
         <v>-0</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D145" s="35" t="s">
-        <v>782</v>
+        <v>759</v>
       </c>
       <c r="E145" s="35"/>
       <c r="F145" s="35"/>
@@ -12968,17 +12757,17 @@
     </row>
     <row r="146" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="10" t="s">
-        <v>784</v>
+        <v>761</v>
       </c>
       <c r="B146" s="31" t="n">
         <f aca="false">-B129*B133</f>
         <v>-0</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D146" s="35" t="s">
-        <v>782</v>
+        <v>759</v>
       </c>
       <c r="E146" s="35"/>
       <c r="F146" s="35"/>
@@ -12991,14 +12780,14 @@
     </row>
     <row r="147" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="10" t="s">
-        <v>785</v>
+        <v>762</v>
       </c>
       <c r="B147" s="31" t="n">
         <f aca="false">-B129*B136</f>
         <v>-0</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D147" s="35"/>
       <c r="E147" s="35"/>
@@ -13012,17 +12801,17 @@
     </row>
     <row r="148" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="38" t="s">
-        <v>786</v>
+        <v>763</v>
       </c>
       <c r="B148" s="31" t="n">
         <f aca="false">B143+B144+B145+B146+B147</f>
         <v>0</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D148" s="35" t="s">
-        <v>787</v>
+        <v>764</v>
       </c>
       <c r="E148" s="35"/>
       <c r="F148" s="35"/>
@@ -13035,17 +12824,17 @@
     </row>
     <row r="149" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="10" t="s">
-        <v>788</v>
+        <v>765</v>
       </c>
       <c r="B149" s="18" t="n">
         <f aca="false">-B123</f>
         <v>-0</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D149" s="35" t="s">
-        <v>789</v>
+        <v>766</v>
       </c>
       <c r="E149" s="35"/>
       <c r="F149" s="35"/>
@@ -13058,17 +12847,17 @@
     </row>
     <row r="150" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="38" t="s">
-        <v>790</v>
+        <v>767</v>
       </c>
       <c r="B150" s="31" t="n">
         <f aca="false">B148+B149</f>
         <v>0</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D150" s="35" t="s">
-        <v>791</v>
+        <v>768</v>
       </c>
       <c r="E150" s="35"/>
       <c r="F150" s="35"/>
@@ -13081,17 +12870,17 @@
     </row>
     <row r="151" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="10" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="B151" s="30" t="n">
         <f aca="false">IF(B148=0,0,B150/B148)</f>
         <v>0</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D151" s="35" t="s">
-        <v>792</v>
+        <v>769</v>
       </c>
       <c r="E151" s="35"/>
       <c r="F151" s="35"/>
@@ -13104,17 +12893,17 @@
     </row>
     <row r="152" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="10" t="s">
-        <v>793</v>
+        <v>770</v>
       </c>
       <c r="B152" s="43" t="n">
         <f aca="false">IF(B123=0,0,B129/B123)</f>
         <v>0</v>
       </c>
       <c r="C152" s="12" t="s">
-        <v>794</v>
+        <v>771</v>
       </c>
       <c r="D152" s="35" t="s">
-        <v>795</v>
+        <v>772</v>
       </c>
       <c r="E152" s="35"/>
       <c r="F152" s="35"/>
@@ -13127,16 +12916,16 @@
     </row>
     <row r="154" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="4" t="s">
-        <v>796</v>
+        <v>773</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="E154" s="4"/>
       <c r="F154" s="4"/>
@@ -13149,14 +12938,14 @@
     </row>
     <row r="155" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="10" t="s">
-        <v>797</v>
+        <v>774</v>
       </c>
       <c r="B155" s="16"/>
       <c r="C155" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D155" s="35" t="s">
-        <v>798</v>
+        <v>775</v>
       </c>
       <c r="E155" s="35"/>
       <c r="F155" s="35"/>
@@ -13169,14 +12958,14 @@
     </row>
     <row r="156" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="10" t="s">
-        <v>799</v>
+        <v>776</v>
       </c>
       <c r="B156" s="16"/>
       <c r="C156" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D156" s="35" t="s">
-        <v>800</v>
+        <v>777</v>
       </c>
       <c r="E156" s="35"/>
       <c r="F156" s="35"/>
@@ -13189,14 +12978,14 @@
     </row>
     <row r="157" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="10" t="s">
-        <v>801</v>
+        <v>778</v>
       </c>
       <c r="B157" s="16"/>
       <c r="C157" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D157" s="35" t="s">
-        <v>802</v>
+        <v>779</v>
       </c>
       <c r="E157" s="35"/>
       <c r="F157" s="35"/>
@@ -13209,17 +12998,17 @@
     </row>
     <row r="158" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="10" t="s">
-        <v>803</v>
+        <v>780</v>
       </c>
       <c r="B158" s="31" t="n">
         <f aca="false">-B129*(B155+B156+B157)</f>
         <v>-0</v>
       </c>
       <c r="C158" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D158" s="35" t="s">
-        <v>804</v>
+        <v>781</v>
       </c>
       <c r="E158" s="35"/>
       <c r="F158" s="35"/>
@@ -13232,17 +13021,17 @@
     </row>
     <row r="159" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="38" t="s">
-        <v>805</v>
+        <v>782</v>
       </c>
       <c r="B159" s="31" t="n">
         <f aca="false">B150+B158</f>
         <v>0</v>
       </c>
       <c r="C159" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D159" s="35" t="s">
-        <v>806</v>
+        <v>783</v>
       </c>
       <c r="E159" s="35"/>
       <c r="F159" s="35"/>
@@ -13255,17 +13044,17 @@
     </row>
     <row r="160" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="10" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="B160" s="30" t="n">
         <f aca="false">IF(B148=0,0,B159/B148)</f>
         <v>0</v>
       </c>
       <c r="C160" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D160" s="35" t="s">
-        <v>807</v>
+        <v>784</v>
       </c>
       <c r="E160" s="35"/>
       <c r="F160" s="35"/>
@@ -13278,7 +13067,7 @@
     </row>
     <row r="162" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
-        <v>808</v>
+        <v>785</v>
       </c>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -13294,7 +13083,7 @@
     </row>
     <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="42" t="s">
-        <v>809</v>
+        <v>786</v>
       </c>
       <c r="B163" s="42"/>
       <c r="C163" s="42"/>
@@ -13327,13 +13116,13 @@
         <v>42</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="E165" s="4"/>
       <c r="F165" s="4"/>
@@ -13346,14 +13135,14 @@
     </row>
     <row r="166" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="10" t="s">
-        <v>810</v>
+        <v>787</v>
       </c>
       <c r="B166" s="27"/>
       <c r="C166" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D166" s="35" t="s">
-        <v>811</v>
+        <v>788</v>
       </c>
       <c r="E166" s="35"/>
       <c r="F166" s="35"/>
@@ -13366,14 +13155,14 @@
     </row>
     <row r="167" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="10" t="s">
-        <v>812</v>
+        <v>789</v>
       </c>
       <c r="B167" s="16"/>
       <c r="C167" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D167" s="35" t="s">
-        <v>813</v>
+        <v>790</v>
       </c>
       <c r="E167" s="35"/>
       <c r="F167" s="35"/>
@@ -13386,17 +13175,17 @@
     </row>
     <row r="168" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="10" t="s">
-        <v>814</v>
+        <v>791</v>
       </c>
       <c r="B168" s="31" t="n">
         <f aca="false">IFERROR(B166/(1+B167),0)</f>
         <v>0</v>
       </c>
       <c r="C168" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D168" s="35" t="s">
-        <v>815</v>
+        <v>792</v>
       </c>
       <c r="E168" s="35"/>
       <c r="F168" s="35"/>
@@ -13409,17 +13198,17 @@
     </row>
     <row r="169" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="10" t="s">
-        <v>816</v>
+        <v>793</v>
       </c>
       <c r="B169" s="33" t="n">
         <f aca="false">IF(B135=0,1+B130,(1+B130)*(1+(1+B134)*B135)-B131)</f>
         <v>1</v>
       </c>
       <c r="C169" s="12" t="s">
-        <v>817</v>
+        <v>794</v>
       </c>
       <c r="D169" s="35" t="s">
-        <v>818</v>
+        <v>795</v>
       </c>
       <c r="E169" s="35"/>
       <c r="F169" s="35"/>
@@ -13432,17 +13221,17 @@
     </row>
     <row r="170" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="10" t="s">
-        <v>819</v>
+        <v>796</v>
       </c>
       <c r="B170" s="31" t="n">
         <f aca="false">IFERROR(B168/B169,0)</f>
         <v>0</v>
       </c>
       <c r="C170" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D170" s="35" t="s">
-        <v>820</v>
+        <v>797</v>
       </c>
       <c r="E170" s="35"/>
       <c r="F170" s="35"/>
@@ -13455,17 +13244,17 @@
     </row>
     <row r="171" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="10" t="s">
-        <v>821</v>
+        <v>798</v>
       </c>
       <c r="B171" s="30" t="str">
         <f aca="false">IF(B170=0,"",IFERROR(B129/B170-1,""))</f>
         <v/>
       </c>
       <c r="C171" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D171" s="35" t="s">
-        <v>822</v>
+        <v>799</v>
       </c>
       <c r="E171" s="35"/>
       <c r="F171" s="35"/>
@@ -13478,17 +13267,17 @@
     </row>
     <row r="172" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="10" t="s">
-        <v>823</v>
+        <v>800</v>
       </c>
       <c r="B172" s="19" t="n">
-        <f aca="false">'1. Briefing'!B30</f>
+        <f aca="false">'1. Briefing'!B27</f>
         <v>0</v>
       </c>
       <c r="C172" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D172" s="35" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="E172" s="35"/>
       <c r="F172" s="35"/>
@@ -13501,17 +13290,17 @@
     </row>
     <row r="173" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="10" t="s">
-        <v>824</v>
+        <v>801</v>
       </c>
       <c r="B173" s="33" t="n">
         <f aca="false">(1-B131-B132-B133-B136-B155-B156-B157)-B172*(1-B131-B132-B133-B136)</f>
         <v>0.9075</v>
       </c>
       <c r="C173" s="12" t="s">
-        <v>825</v>
+        <v>802</v>
       </c>
       <c r="D173" s="35" t="s">
-        <v>826</v>
+        <v>803</v>
       </c>
       <c r="E173" s="35"/>
       <c r="F173" s="35"/>
@@ -13524,17 +13313,17 @@
     </row>
     <row r="174" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="10" t="s">
-        <v>827</v>
+        <v>804</v>
       </c>
       <c r="B174" s="31" t="n">
         <f aca="false">IF(B173&lt;=0,"Inviável",IFERROR(B123/B173,0))</f>
         <v>0</v>
       </c>
       <c r="C174" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D174" s="35" t="s">
-        <v>828</v>
+        <v>805</v>
       </c>
       <c r="E174" s="35"/>
       <c r="F174" s="35"/>
@@ -13547,17 +13336,17 @@
     </row>
     <row r="175" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="10" t="s">
-        <v>829</v>
+        <v>806</v>
       </c>
       <c r="B175" s="31" t="n">
         <f aca="false">IF(B173&lt;=0,"Inviável",IFERROR(B174*B169,0))</f>
         <v>0</v>
       </c>
       <c r="C175" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D175" s="35" t="s">
-        <v>830</v>
+        <v>807</v>
       </c>
       <c r="E175" s="35"/>
       <c r="F175" s="35"/>
@@ -13570,17 +13359,17 @@
     </row>
     <row r="176" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="10" t="s">
-        <v>831</v>
+        <v>808</v>
       </c>
       <c r="B176" s="31" t="n">
         <f aca="false">IF(B173&lt;=0,"Inviável",IFERROR(B175*(1+B167),0))</f>
         <v>0</v>
       </c>
       <c r="C176" s="12" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="D176" s="35" t="s">
-        <v>832</v>
+        <v>809</v>
       </c>
       <c r="E176" s="35"/>
       <c r="F176" s="35"/>
@@ -13593,7 +13382,7 @@
     </row>
     <row r="177" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="38" t="s">
-        <v>833</v>
+        <v>810</v>
       </c>
       <c r="B177" s="5" t="str">
         <f aca="false">IF(B148=0,"Preencha as premissas",IF(B172=0,"Defina a margem-alvo no briefing",IF(B160&gt;=B172,"APROVADO — margem acima do alvo",IF(B160&gt;=B172*0.9,"ATENÇÃO — até 10% abaixo do alvo","REPROVADO — margem insuficiente"))))</f>
@@ -13601,7 +13390,7 @@
       </c>
       <c r="C177" s="12"/>
       <c r="D177" s="35" t="s">
-        <v>834</v>
+        <v>811</v>
       </c>
       <c r="E177" s="35"/>
       <c r="F177" s="35"/>
@@ -13614,7 +13403,7 @@
     </row>
     <row r="179" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="3" t="s">
-        <v>835</v>
+        <v>812</v>
       </c>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -13633,13 +13422,13 @@
         <v>42</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="E180" s="4"/>
       <c r="F180" s="4"/>
@@ -13652,14 +13441,14 @@
     </row>
     <row r="181" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="10" t="s">
-        <v>836</v>
+        <v>813</v>
       </c>
       <c r="B181" s="15"/>
       <c r="C181" s="12" t="s">
-        <v>837</v>
+        <v>814</v>
       </c>
       <c r="D181" s="35" t="s">
-        <v>838</v>
+        <v>815</v>
       </c>
       <c r="E181" s="35"/>
       <c r="F181" s="35"/>
@@ -13672,14 +13461,14 @@
     </row>
     <row r="182" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="10" t="s">
-        <v>839</v>
+        <v>816</v>
       </c>
       <c r="B182" s="15"/>
       <c r="C182" s="12" t="s">
-        <v>837</v>
+        <v>814</v>
       </c>
       <c r="D182" s="35" t="s">
-        <v>840</v>
+        <v>817</v>
       </c>
       <c r="E182" s="35"/>
       <c r="F182" s="35"/>
@@ -13692,17 +13481,17 @@
     </row>
     <row r="183" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="10" t="s">
-        <v>841</v>
+        <v>818</v>
       </c>
       <c r="B183" s="28" t="n">
         <f aca="false">B181+B182</f>
         <v>0</v>
       </c>
       <c r="C183" s="12" t="s">
-        <v>837</v>
+        <v>814</v>
       </c>
       <c r="D183" s="35" t="s">
-        <v>842</v>
+        <v>819</v>
       </c>
       <c r="E183" s="35"/>
       <c r="F183" s="35"/>
@@ -13715,17 +13504,17 @@
     </row>
     <row r="184" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="10" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="B184" s="25" t="n">
         <f aca="false">IF(B159&lt;=0,0,B183/B159)</f>
         <v>0</v>
       </c>
       <c r="C184" s="12" t="s">
-        <v>843</v>
+        <v>820</v>
       </c>
       <c r="D184" s="35" t="s">
-        <v>844</v>
+        <v>821</v>
       </c>
       <c r="E184" s="35"/>
       <c r="F184" s="35"/>
@@ -13738,17 +13527,17 @@
     </row>
     <row r="185" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="10" t="s">
-        <v>845</v>
+        <v>822</v>
       </c>
       <c r="B185" s="21" t="n">
-        <f aca="false">IFERROR('1. Briefing'!B28/12,0)</f>
+        <f aca="false">IFERROR('1. Briefing'!B25/12,0)</f>
         <v>0</v>
       </c>
       <c r="C185" s="12" t="s">
-        <v>843</v>
+        <v>820</v>
       </c>
       <c r="D185" s="35" t="s">
-        <v>846</v>
+        <v>823</v>
       </c>
       <c r="E185" s="35"/>
       <c r="F185" s="35"/>
@@ -13761,17 +13550,17 @@
     </row>
     <row r="186" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="10" t="s">
-        <v>847</v>
+        <v>824</v>
       </c>
       <c r="B186" s="30" t="n">
         <f aca="false">IF(B184=0,0,B185/B184-1)</f>
         <v>0</v>
       </c>
       <c r="C186" s="12" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D186" s="35" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="E186" s="35"/>
       <c r="F186" s="35"/>
@@ -13784,17 +13573,17 @@
     </row>
     <row r="187" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="10" t="s">
-        <v>849</v>
+        <v>826</v>
       </c>
       <c r="B187" s="33" t="n">
         <f aca="false">IFERROR(B185/B10,0)</f>
         <v>0</v>
       </c>
       <c r="C187" s="12" t="s">
-        <v>850</v>
+        <v>827</v>
       </c>
       <c r="D187" s="35" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
       <c r="E187" s="35"/>
       <c r="F187" s="35"/>
@@ -13807,7 +13596,7 @@
     </row>
     <row r="189" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="s">
-        <v>852</v>
+        <v>829</v>
       </c>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -13823,31 +13612,31 @@
     </row>
     <row r="190" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="4" t="s">
-        <v>853</v>
+        <v>830</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>854</v>
+        <v>831</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>855</v>
+        <v>832</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>856</v>
+        <v>833</v>
       </c>
       <c r="E190" s="4" t="s">
-        <v>857</v>
+        <v>834</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>858</v>
+        <v>835</v>
       </c>
       <c r="G190" s="4" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
       <c r="H190" s="4" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="I190" s="4" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="J190" s="4"/>
       <c r="K190" s="4"/>
@@ -13855,7 +13644,7 @@
     </row>
     <row r="191" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="10" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
       <c r="B191" s="16" t="n">
         <v>-0.1</v>
@@ -13890,7 +13679,7 @@
     </row>
     <row r="192" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="10" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
       <c r="B192" s="16" t="n">
         <v>-0.1</v>
@@ -13925,7 +13714,7 @@
     </row>
     <row r="193" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="10" t="s">
-        <v>862</v>
+        <v>839</v>
       </c>
       <c r="B193" s="16" t="n">
         <v>0</v>
@@ -13960,7 +13749,7 @@
     </row>
     <row r="194" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="10" t="s">
-        <v>863</v>
+        <v>840</v>
       </c>
       <c r="B194" s="16" t="n">
         <v>0</v>
@@ -13995,7 +13784,7 @@
     </row>
     <row r="195" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="10" t="s">
-        <v>864</v>
+        <v>841</v>
       </c>
       <c r="B195" s="16" t="n">
         <v>0.05</v>
@@ -14030,7 +13819,7 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="29" t="s">
-        <v>865</v>
+        <v>842</v>
       </c>
       <c r="B196" s="32"/>
       <c r="C196" s="32"/>
@@ -14049,7 +13838,7 @@
     </row>
     <row r="197" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="42" t="s">
-        <v>866</v>
+        <v>843</v>
       </c>
       <c r="B197" s="42"/>
       <c r="C197" s="42"/>
@@ -14230,7 +14019,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>867</v>
+        <v>844</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -14240,7 +14029,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>868</v>
+        <v>845</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -14250,7 +14039,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>869</v>
+        <v>846</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -14260,21 +14049,21 @@
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>870</v>
+        <v>847</v>
       </c>
       <c r="B6" s="16" t="n">
         <v>0.25</v>
@@ -14283,12 +14072,12 @@
       <c r="D6" s="32"/>
       <c r="E6" s="32"/>
       <c r="F6" s="12" t="s">
-        <v>871</v>
+        <v>848</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>872</v>
+        <v>849</v>
       </c>
       <c r="B7" s="16" t="n">
         <v>0.15</v>
@@ -14297,12 +14086,12 @@
       <c r="D7" s="32"/>
       <c r="E7" s="32"/>
       <c r="F7" s="12" t="s">
-        <v>873</v>
+        <v>850</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>874</v>
+        <v>851</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>0.08</v>
@@ -14311,12 +14100,12 @@
       <c r="D8" s="32"/>
       <c r="E8" s="32"/>
       <c r="F8" s="12" t="s">
-        <v>875</v>
+        <v>852</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>876</v>
+        <v>853</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>0.06</v>
@@ -14325,12 +14114,12 @@
       <c r="D9" s="32"/>
       <c r="E9" s="32"/>
       <c r="F9" s="12" t="s">
-        <v>877</v>
+        <v>854</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>878</v>
+        <v>855</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>0.18</v>
@@ -14339,29 +14128,29 @@
       <c r="D10" s="32"/>
       <c r="E10" s="32"/>
       <c r="F10" s="12" t="s">
-        <v>879</v>
+        <v>856</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>880</v>
+        <v>857</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
       <c r="E11" s="32"/>
       <c r="F11" s="12" t="s">
-        <v>881</v>
+        <v>858</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>882</v>
+        <v>859</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>883</v>
+        <v>860</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -14371,31 +14160,31 @@
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>884</v>
+        <v>861</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>885</v>
+        <v>862</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>886</v>
+        <v>863</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>887</v>
+        <v>864</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>888</v>
+        <v>865</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>889</v>
+        <v>866</v>
       </c>
       <c r="B16" s="44"/>
       <c r="C16" s="21" t="n">
-        <f aca="false">IFERROR('1. Briefing'!B28,0)</f>
+        <f aca="false">IFERROR('1. Briefing'!B25,0)</f>
         <v>0</v>
       </c>
       <c r="D16" s="21" t="n">
@@ -14407,12 +14196,12 @@
         <v>0</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>890</v>
+        <v>867</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>891</v>
+        <v>868</v>
       </c>
       <c r="B17" s="44"/>
       <c r="C17" s="18" t="n">
@@ -14428,12 +14217,12 @@
         <v>0</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>892</v>
+        <v>869</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>779</v>
+        <v>756</v>
       </c>
       <c r="B18" s="44"/>
       <c r="C18" s="28" t="n">
@@ -14449,12 +14238,12 @@
         <v>0</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>893</v>
+        <v>870</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>894</v>
+        <v>871</v>
       </c>
       <c r="B19" s="44"/>
       <c r="C19" s="17" t="n">
@@ -14470,12 +14259,12 @@
         <v>0</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>895</v>
+        <v>872</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>896</v>
+        <v>873</v>
       </c>
       <c r="B20" s="44"/>
       <c r="C20" s="17" t="n">
@@ -14491,12 +14280,12 @@
         <v>-0</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>897</v>
+        <v>874</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="s">
-        <v>898</v>
+        <v>875</v>
       </c>
       <c r="B21" s="44"/>
       <c r="C21" s="28" t="n">
@@ -14512,12 +14301,12 @@
         <v>0</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>899</v>
+        <v>876</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>900</v>
+        <v>877</v>
       </c>
       <c r="B22" s="44"/>
       <c r="C22" s="28" t="n">
@@ -14533,12 +14322,12 @@
         <v>-0</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>901</v>
+        <v>878</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>902</v>
+        <v>879</v>
       </c>
       <c r="B23" s="44"/>
       <c r="C23" s="28" t="n">
@@ -14554,12 +14343,12 @@
         <v>-0</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>901</v>
+        <v>878</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="38" t="s">
-        <v>903</v>
+        <v>880</v>
       </c>
       <c r="B24" s="44"/>
       <c r="C24" s="28" t="n">
@@ -14575,12 +14364,12 @@
         <v>0</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>904</v>
+        <v>881</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>905</v>
+        <v>882</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -14590,27 +14379,27 @@
     </row>
     <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>884</v>
+        <v>861</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>885</v>
+        <v>862</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>886</v>
+        <v>863</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>887</v>
+        <v>864</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>888</v>
+        <v>865</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>906</v>
+        <v>883</v>
       </c>
       <c r="B28" s="17" t="n">
         <f aca="false">'4. Embalagem'!H15</f>
@@ -14620,12 +14409,12 @@
       <c r="D28" s="44"/>
       <c r="E28" s="44"/>
       <c r="F28" s="12" t="s">
-        <v>907</v>
+        <v>884</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>908</v>
+        <v>885</v>
       </c>
       <c r="B29" s="17" t="n">
         <f aca="false">'3. Formulação'!F35</f>
@@ -14635,12 +14424,12 @@
       <c r="D29" s="44"/>
       <c r="E29" s="44"/>
       <c r="F29" s="12" t="s">
-        <v>909</v>
+        <v>886</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>910</v>
+        <v>887</v>
       </c>
       <c r="B30" s="17" t="n">
         <f aca="false">'3. Formulação'!B76</f>
@@ -14650,12 +14439,12 @@
       <c r="D30" s="44"/>
       <c r="E30" s="44"/>
       <c r="F30" s="12" t="s">
-        <v>909</v>
+        <v>886</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>911</v>
+        <v>888</v>
       </c>
       <c r="B31" s="17" t="n">
         <f aca="false">'4. Embalagem'!G18</f>
@@ -14665,12 +14454,12 @@
       <c r="D31" s="44"/>
       <c r="E31" s="44"/>
       <c r="F31" s="12" t="s">
-        <v>912</v>
+        <v>889</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>913</v>
+        <v>890</v>
       </c>
       <c r="B32" s="17" t="n">
         <f aca="false">$B$11</f>
@@ -14680,12 +14469,12 @@
       <c r="D32" s="44"/>
       <c r="E32" s="44"/>
       <c r="F32" s="12" t="s">
-        <v>914</v>
+        <v>891</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="38" t="s">
-        <v>915</v>
+        <v>892</v>
       </c>
       <c r="B33" s="28" t="n">
         <f aca="false">SUM(B28:B32)</f>
@@ -14695,12 +14484,12 @@
       <c r="D33" s="44"/>
       <c r="E33" s="44"/>
       <c r="F33" s="12" t="s">
-        <v>916</v>
+        <v>893</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>917</v>
+        <v>894</v>
       </c>
       <c r="B34" s="28" t="n">
         <f aca="false">-B33</f>
@@ -14719,12 +14508,12 @@
         <v>0</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>918</v>
+        <v>895</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="38" t="s">
-        <v>919</v>
+        <v>896</v>
       </c>
       <c r="B35" s="28" t="n">
         <f aca="false">B34</f>
@@ -14743,12 +14532,12 @@
         <v>-5114</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>920</v>
+        <v>897</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>921</v>
+        <v>898</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -14758,10 +14547,10 @@
     </row>
     <row r="38" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>922</v>
+        <v>899</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -14772,7 +14561,7 @@
     </row>
     <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>923</v>
+        <v>900</v>
       </c>
       <c r="B39" s="28" t="n">
         <f aca="false">IFERROR(NPV($B$10,C34:E34)+B34,0)</f>
@@ -14782,12 +14571,12 @@
       <c r="D39" s="32"/>
       <c r="E39" s="32"/>
       <c r="F39" s="12" t="s">
-        <v>924</v>
+        <v>901</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>925</v>
+        <v>902</v>
       </c>
       <c r="B40" s="30" t="str">
         <f aca="false">IFERROR(IRR(B34:E34),"n/d")</f>
@@ -14797,12 +14586,12 @@
       <c r="D40" s="32"/>
       <c r="E40" s="32"/>
       <c r="F40" s="12" t="s">
-        <v>926</v>
+        <v>903</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="B41" s="33" t="str">
         <f aca="false">IF(B35&gt;=0,0,IF(C35&gt;=0,IFERROR(-B34/C34,""),IF(D35&gt;=0,IFERROR(1-C35/D34,""),IF(E35&gt;=0,IFERROR(2-D35/E34,""),"Acima de 3 anos"))))</f>
@@ -14812,12 +14601,12 @@
       <c r="D41" s="32"/>
       <c r="E41" s="32"/>
       <c r="F41" s="12" t="s">
-        <v>927</v>
+        <v>904</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>928</v>
+        <v>905</v>
       </c>
       <c r="B42" s="30" t="n">
         <f aca="false">IF(B33=0,0,(SUM(C34:E34)-B33)/B33)</f>
@@ -14827,27 +14616,27 @@
       <c r="D42" s="32"/>
       <c r="E42" s="32"/>
       <c r="F42" s="12" t="s">
-        <v>929</v>
+        <v>906</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>930</v>
+        <v>907</v>
       </c>
       <c r="B43" s="5" t="str">
-        <f aca="false">IF('1. Briefing'!B67="","Capex não informado no briefing",IF(B33&lt;='1. Briefing'!B67,"Dentro do teto autorizado","ESTOURA o teto autorizado"))</f>
+        <f aca="false">IF('1. Briefing'!B29="","Capex não informado no briefing",IF(B33&lt;='1. Briefing'!B29,"Dentro do teto autorizado","ESTOURA o teto autorizado"))</f>
         <v>Capex não informado no briefing</v>
       </c>
       <c r="C43" s="32"/>
       <c r="D43" s="32"/>
       <c r="E43" s="32"/>
       <c r="F43" s="12" t="s">
-        <v>931</v>
+        <v>908</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>932</v>
+        <v>909</v>
       </c>
       <c r="B44" s="30" t="n">
         <f aca="false">IF(C19=0,0,C21/C19)</f>
@@ -14857,7 +14646,7 @@
       <c r="D44" s="32"/>
       <c r="E44" s="32"/>
       <c r="F44" s="12" t="s">
-        <v>933</v>
+        <v>910</v>
       </c>
     </row>
   </sheetData>
@@ -14885,7 +14674,7 @@
     <tabColor rgb="FFEC008C"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -14896,7 +14685,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>934</v>
+        <v>911</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -14905,7 +14694,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>935</v>
+        <v>912</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -14914,7 +14703,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>936</v>
+        <v>913</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -14923,27 +14712,27 @@
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>937</v>
+        <v>914</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>938</v>
+        <v>915</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>939</v>
+        <v>916</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>940</v>
+        <v>917</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>941</v>
+        <v>918</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>942</v>
+        <v>919</v>
       </c>
       <c r="B6" s="16" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="33" t="str">
@@ -14951,15 +14740,15 @@
         <v/>
       </c>
       <c r="E6" s="12" t="s">
-        <v>943</v>
+        <v>920</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>944</v>
+        <v>921</v>
       </c>
       <c r="B7" s="16" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="33" t="str">
@@ -14967,15 +14756,15 @@
         <v/>
       </c>
       <c r="E7" s="12" t="s">
-        <v>945</v>
+        <v>922</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>946</v>
+        <v>923</v>
       </c>
       <c r="B8" s="16" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="33" t="str">
@@ -14983,15 +14772,15 @@
         <v/>
       </c>
       <c r="E8" s="12" t="s">
-        <v>947</v>
+        <v>924</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>948</v>
+        <v>925</v>
       </c>
       <c r="B9" s="16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="33" t="str">
@@ -14999,15 +14788,15 @@
         <v/>
       </c>
       <c r="E9" s="12" t="s">
-        <v>949</v>
+        <v>926</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>950</v>
+        <v>927</v>
       </c>
       <c r="B10" s="16" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="33" t="str">
@@ -15015,12 +14804,12 @@
         <v/>
       </c>
       <c r="E10" s="12" t="s">
-        <v>951</v>
+        <v>928</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>952</v>
+        <v>929</v>
       </c>
       <c r="B11" s="16" t="n">
         <v>0.08</v>
@@ -15031,165 +14820,129 @@
         <v/>
       </c>
       <c r="E11" s="12" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
-        <v>954</v>
-      </c>
-      <c r="B12" s="16" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="33" t="str">
-        <f aca="false">IF(C12="","",B12*C12)</f>
-        <v/>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
-        <v>956</v>
-      </c>
-      <c r="B13" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="33" t="str">
-        <f aca="false">IF(C13="","",B13*C13)</f>
-        <v/>
+        <v>930</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="29" t="s">
+        <v>931</v>
+      </c>
+      <c r="B12" s="30" t="n">
+        <f aca="false">SUM(B6:B11)</f>
+        <v>1</v>
+      </c>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="5" t="str">
+        <f aca="false">IF(ABS(B12-1)&lt;0.0001,"OK — pesos somam 100%","AJUSTAR — os pesos precisam somar 100%")</f>
+        <v>OK — pesos somam 100%</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="41" t="s">
+        <v>932</v>
+      </c>
+      <c r="B13" s="32"/>
+      <c r="C13" s="25" t="n">
+        <f aca="false">COUNT(C6:C11)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="33" t="n">
+        <f aca="false">IFERROR(SUMPRODUCT(B6:B11,C6:C11),0)</f>
+        <v>0</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>958</v>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="33" t="str">
-        <f aca="false">IF(C14="","",B14*C14)</f>
-        <v/>
-      </c>
+        <v>933</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="41" t="s">
+        <v>934</v>
+      </c>
+      <c r="B14" s="36" t="str">
+        <f aca="false">IF(COUNT(C6:C11)&lt;6,"Incompleto — pontue todos os critérios",IF(D13&gt;=4,"PRIORIDADE MÁXIMA — entra na fila agora",IF(D13&gt;=3.2,"APROVADO — entra na fila conforme capacidade",IF(D13&gt;=2.5,"REVISAR — reformular conceito, custo ou escopo","DESCARTAR — não justifica o esforço"))))</f>
+        <v>Incompleto — pontue todos os critérios</v>
+      </c>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
       <c r="E14" s="12" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
-        <v>960</v>
-      </c>
-      <c r="B15" s="16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="33" t="str">
-        <f aca="false">IF(C15="","",B15*C15)</f>
-        <v/>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="29" t="s">
-        <v>962</v>
-      </c>
-      <c r="B16" s="30" t="n">
-        <f aca="false">SUM(B6:B15)</f>
-        <v>1</v>
-      </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="5" t="str">
-        <f aca="false">IF(ABS(B16-1)&lt;0.0001,"OK — pesos somam 100%","AJUSTAR — os pesos precisam somar 100%")</f>
-        <v>OK — pesos somam 100%</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="41" t="s">
-        <v>963</v>
-      </c>
-      <c r="B17" s="32"/>
-      <c r="C17" s="25" t="n">
-        <f aca="false">COUNT(C6:C15)</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="33" t="n">
-        <f aca="false">IFERROR(SUMPRODUCT(B6:B15,C6:C15),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="41" t="s">
-        <v>965</v>
-      </c>
-      <c r="B18" s="36" t="str">
-        <f aca="false">IF(COUNT(C6:C15)&lt;10,"Incompleto — pontue todos os critérios",IF(D17&gt;=4,"PRIORIDADE MÁXIMA — entra na fila agora",IF(D17&gt;=3.2,"APROVADO — entra na fila conforme capacidade",IF(D17&gt;=2.5,"REVISAR — reformular conceito, custo ou escopo","DESCARTAR — não justifica o esforço"))))</f>
-        <v>Incompleto — pontue todos os critérios</v>
-      </c>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="12" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>967</v>
-      </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-    </row>
-    <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>968</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>969</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>970</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
-        <v>971</v>
-      </c>
-      <c r="B22" s="33" t="n">
-        <f aca="false">D17</f>
-        <v>0</v>
-      </c>
-      <c r="C22" s="17" t="n">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10" t="s">
+        <v>940</v>
+      </c>
+      <c r="B18" s="33" t="n">
+        <f aca="false">D13</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="17" t="n">
         <f aca="false">'6. Viabilidade'!B33</f>
         <v>5114</v>
       </c>
-      <c r="D22" s="22" t="str">
+      <c r="D18" s="22" t="str">
         <f aca="false">'6. Viabilidade'!B41</f>
         <v>Acima de 3 anos</v>
       </c>
-      <c r="E22" s="5" t="str">
-        <f aca="false">B18</f>
+      <c r="E18" s="5" t="str">
+        <f aca="false">B14</f>
         <v>Incompleto — pontue todos os critérios</v>
       </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="11"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="11"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="11"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11"/>
@@ -15205,46 +14958,18 @@
       <c r="D24" s="26"/>
       <c r="E24" s="11"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="11"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="11"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11"/>
-      <c r="B27" s="26"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="11"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11"/>
-      <c r="B28" s="26"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="11"/>
-    </row>
-    <row r="29" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="29" t="s">
-        <v>972</v>
-      </c>
-      <c r="B29" s="25" t="n">
-        <f aca="false">IFERROR(RANK(B22,B22:B28,0),0)</f>
+    <row r="25" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="29" t="s">
+        <v>941</v>
+      </c>
+      <c r="B25" s="25" t="n">
+        <f aca="false">IFERROR(RANK(B18,B18:B24,0),0)</f>
         <v>1</v>
       </c>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="12" t="s">
-        <v>973</v>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="12" t="s">
+        <v>942</v>
       </c>
     </row>
   </sheetData>
@@ -15252,11 +14977,11 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="A16:E16"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C6:C15" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C6:C11" type="list">
       <formula1>"1,2,3,4,5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -15290,7 +15015,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>974</v>
+        <v>943</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -15303,7 +15028,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>975</v>
+        <v>944</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -15316,7 +15041,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>976</v>
+        <v>945</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -15330,16 +15055,16 @@
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
@@ -15347,21 +15072,21 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="45"/>
       <c r="B6" s="10" t="s">
-        <v>977</v>
+        <v>946</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="32"/>
       <c r="E6" s="32"/>
       <c r="F6" s="32"/>
       <c r="G6" s="35" t="s">
-        <v>978</v>
+        <v>947</v>
       </c>
       <c r="H6" s="35"/>
       <c r="I6" s="35"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>979</v>
+        <v>948</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -15377,28 +15102,28 @@
         <v>3</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>981</v>
+        <v>950</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>982</v>
+        <v>951</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>983</v>
+        <v>952</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>984</v>
+        <v>953</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>985</v>
+        <v>954</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>986</v>
+        <v>955</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15406,10 +15131,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>987</v>
+        <v>956</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>988</v>
+        <v>957</v>
       </c>
       <c r="D10" s="46" t="str">
         <f aca="false">IF($C$6="","",$C$6)</f>
@@ -15433,10 +15158,10 @@
         <v>2</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>989</v>
+        <v>958</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>990</v>
+        <v>959</v>
       </c>
       <c r="D11" s="46" t="str">
         <f aca="false">IF(F10="","",F10+1)</f>
@@ -15460,10 +15185,10 @@
         <v>3</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>991</v>
+        <v>960</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>990</v>
+        <v>959</v>
       </c>
       <c r="D12" s="46" t="str">
         <f aca="false">IF(F11="","",F11+1)</f>
@@ -15487,10 +15212,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>992</v>
+        <v>961</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>993</v>
+        <v>962</v>
       </c>
       <c r="D13" s="46" t="str">
         <f aca="false">IF(F12="","",F12+1)</f>
@@ -15514,10 +15239,10 @@
         <v>5</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>994</v>
+        <v>963</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>993</v>
+        <v>962</v>
       </c>
       <c r="D14" s="46" t="str">
         <f aca="false">IF(F13="","",F13+1)</f>
@@ -15541,10 +15266,10 @@
         <v>6</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>995</v>
+        <v>964</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>996</v>
+        <v>965</v>
       </c>
       <c r="D15" s="46" t="str">
         <f aca="false">IF(F14="","",F14+1)</f>
@@ -15568,10 +15293,10 @@
         <v>7</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>997</v>
+        <v>966</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>998</v>
+        <v>967</v>
       </c>
       <c r="D16" s="46" t="str">
         <f aca="false">IF(F15="","",F15+1)</f>
@@ -15595,10 +15320,10 @@
         <v>8</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>999</v>
+        <v>968</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1000</v>
+        <v>969</v>
       </c>
       <c r="D17" s="46" t="str">
         <f aca="false">IF(F16="","",F16+1)</f>
@@ -15622,10 +15347,10 @@
         <v>9</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1001</v>
+        <v>970</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>1002</v>
+        <v>971</v>
       </c>
       <c r="D18" s="46" t="str">
         <f aca="false">IF(F17="","",F17+1)</f>
@@ -15649,10 +15374,10 @@
         <v>10</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1003</v>
+        <v>972</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>1004</v>
+        <v>973</v>
       </c>
       <c r="D19" s="46" t="str">
         <f aca="false">IF(F18="","",F18+1)</f>
@@ -15676,10 +15401,10 @@
         <v>11</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1005</v>
+        <v>974</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>1006</v>
+        <v>975</v>
       </c>
       <c r="D20" s="46" t="str">
         <f aca="false">IF(F19="","",F19+1)</f>
@@ -15703,10 +15428,10 @@
         <v>12</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1007</v>
+        <v>976</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>1008</v>
+        <v>977</v>
       </c>
       <c r="D21" s="46" t="str">
         <f aca="false">IF(F20="","",F20+1)</f>
@@ -15730,10 +15455,10 @@
         <v>13</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1009</v>
+        <v>978</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>1010</v>
+        <v>979</v>
       </c>
       <c r="D22" s="46" t="str">
         <f aca="false">IF(F21="","",F21+1)</f>
@@ -15757,10 +15482,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1011</v>
+        <v>980</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>1012</v>
+        <v>981</v>
       </c>
       <c r="D23" s="46" t="str">
         <f aca="false">IF(F22="","",F22+1)</f>
@@ -15784,10 +15509,10 @@
         <v>15</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1013</v>
+        <v>982</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>1014</v>
+        <v>983</v>
       </c>
       <c r="D24" s="46" t="str">
         <f aca="false">IF(F23="","",F23+1)</f>
@@ -15811,10 +15536,10 @@
         <v>16</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>1015</v>
+        <v>984</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>1016</v>
+        <v>985</v>
       </c>
       <c r="D25" s="46" t="str">
         <f aca="false">IF(F24="","",F24+1)</f>
@@ -15836,7 +15561,7 @@
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="32"/>
       <c r="B26" s="29" t="s">
-        <v>1017</v>
+        <v>986</v>
       </c>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
@@ -15849,7 +15574,7 @@
         <v/>
       </c>
       <c r="G26" s="12" t="s">
-        <v>1018</v>
+        <v>987</v>
       </c>
       <c r="H26" s="30" t="n">
         <f aca="false">IFERROR(AVERAGE(H10:H25),0)</f>
@@ -15860,7 +15585,7 @@
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="32"/>
       <c r="B27" s="29" t="s">
-        <v>1019</v>
+        <v>988</v>
       </c>
       <c r="C27" s="32"/>
       <c r="D27" s="32"/>
@@ -15876,7 +15601,7 @@
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="32"/>
       <c r="B28" s="29" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="C28" s="32"/>
       <c r="D28" s="32"/>
@@ -15886,7 +15611,7 @@
         <v/>
       </c>
       <c r="G28" s="35" t="s">
-        <v>1020</v>
+        <v>989</v>
       </c>
       <c r="H28" s="35"/>
       <c r="I28" s="35"/>
@@ -15894,7 +15619,7 @@
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="32"/>
       <c r="B29" s="29" t="s">
-        <v>1021</v>
+        <v>990</v>
       </c>
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
@@ -15904,14 +15629,14 @@
         <v/>
       </c>
       <c r="G29" s="35" t="s">
-        <v>1022</v>
+        <v>991</v>
       </c>
       <c r="H29" s="35"/>
       <c r="I29" s="35"/>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>1023</v>
+        <v>992</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -15924,7 +15649,7 @@
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="47" t="s">
-        <v>1024</v>
+        <v>993</v>
       </c>
       <c r="B32" s="47"/>
       <c r="C32" s="47"/>
